--- a/Danh_Sach_Khach_Hang_Sales_2026.xlsx
+++ b/Danh_Sach_Khach_Hang_Sales_2026.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1462,7 +1462,11 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
@@ -2020,7 +2024,11 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
@@ -2101,7 +2109,11 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -2869,7 +2881,11 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
@@ -3140,7 +3156,11 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
@@ -3223,7 +3243,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>adoption-steps-desktop|1|0|0</t>
+          <t>US</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3306,7 +3326,11 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
@@ -3387,7 +3411,11 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
@@ -3751,7 +3779,11 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
@@ -4222,7 +4254,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>US</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4305,7 +4337,11 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
@@ -4392,7 +4428,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -4776,7 +4812,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5437,7 +5473,11 @@
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
@@ -5611,7 +5651,11 @@
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
@@ -6375,7 +6419,11 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
@@ -6460,7 +6508,11 @@
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
@@ -6820,7 +6872,11 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
@@ -6901,7 +6957,11 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
@@ -7283,7 +7343,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -7758,7 +7818,11 @@
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
@@ -7839,7 +7903,11 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
@@ -8306,7 +8374,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -8393,7 +8461,11 @@
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
@@ -8474,7 +8546,11 @@
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
@@ -9048,7 +9124,11 @@
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
@@ -9139,7 +9219,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>init</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -9226,7 +9306,11 @@
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
@@ -9414,7 +9498,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>menu false  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9598,7 +9682,11 @@
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
@@ -9776,7 +9864,11 @@
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
@@ -10047,7 +10139,11 @@
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
@@ -10221,7 +10317,11 @@
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
@@ -10391,7 +10491,11 @@
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
@@ -10583,7 +10687,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -10769,7 +10873,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -11539,7 +11643,11 @@
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
@@ -11915,7 +12023,11 @@
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
@@ -13075,7 +13187,11 @@
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
@@ -13552,7 +13668,11 @@
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
@@ -13823,7 +13943,11 @@
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
@@ -13910,7 +14034,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -13999,7 +14123,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -14555,7 +14679,11 @@
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
@@ -14739,7 +14867,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -14834,7 +14962,11 @@
       </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
@@ -15022,7 +15154,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -15616,7 +15748,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -15796,7 +15928,11 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
@@ -15962,7 +16098,11 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
@@ -16023,7 +16163,11 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
@@ -16084,7 +16228,11 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
@@ -16157,7 +16305,11 @@
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
@@ -16218,7 +16370,11 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
@@ -16279,7 +16435,11 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
@@ -16340,7 +16500,11 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
@@ -16401,7 +16565,11 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
@@ -16474,7 +16642,11 @@
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
@@ -16535,7 +16707,11 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
@@ -16596,7 +16772,11 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
@@ -16673,7 +16853,11 @@
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
@@ -16750,7 +16934,11 @@
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
@@ -16815,7 +17003,11 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
@@ -16876,7 +17068,11 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
@@ -16937,7 +17133,11 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
@@ -16998,7 +17198,11 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
@@ -17059,7 +17263,11 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
@@ -17120,7 +17328,11 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
@@ -17181,7 +17393,11 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
@@ -17242,7 +17458,11 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
@@ -17303,7 +17523,11 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
@@ -17364,7 +17588,11 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
@@ -17425,7 +17653,11 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
@@ -17486,7 +17718,11 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
@@ -17547,7 +17783,11 @@
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
@@ -17608,7 +17848,11 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
@@ -17669,7 +17913,11 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
@@ -17746,7 +17994,11 @@
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
@@ -17807,7 +18059,11 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
@@ -17868,7 +18124,11 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
@@ -17929,7 +18189,11 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
@@ -17990,7 +18254,11 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
@@ -18051,7 +18319,11 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
@@ -18112,7 +18384,11 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
@@ -18191,7 +18467,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>menu selected  link</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -18262,7 +18538,11 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
@@ -18323,7 +18603,11 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
@@ -18396,7 +18680,11 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
@@ -18457,7 +18745,11 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
@@ -18518,7 +18810,11 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
@@ -18579,7 +18875,11 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
@@ -18640,7 +18940,11 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
@@ -18701,7 +19005,11 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
@@ -18762,7 +19070,11 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
@@ -18823,7 +19135,11 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
@@ -18884,7 +19200,11 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
@@ -18945,7 +19265,11 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
@@ -19006,7 +19330,11 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
@@ -19067,7 +19395,11 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
@@ -19128,7 +19460,11 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
@@ -19189,7 +19525,11 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
@@ -19250,7 +19590,11 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
@@ -19327,7 +19671,11 @@
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
@@ -19388,7 +19736,11 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
@@ -19449,7 +19801,11 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
@@ -19510,7 +19866,11 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
@@ -19571,7 +19931,11 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
@@ -19632,7 +19996,11 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
@@ -19693,7 +20061,11 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
@@ -19754,7 +20126,11 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
@@ -19815,7 +20191,11 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
@@ -19876,7 +20256,11 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
@@ -19937,7 +20321,11 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
@@ -19998,7 +20386,11 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
@@ -20059,7 +20451,11 @@
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
@@ -20136,7 +20532,11 @@
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
@@ -20197,7 +20597,11 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
@@ -20258,7 +20662,11 @@
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
@@ -20319,7 +20727,11 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
@@ -20380,7 +20792,11 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
@@ -20441,7 +20857,11 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
@@ -20502,7 +20922,11 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
@@ -20563,7 +20987,11 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
@@ -20624,7 +21052,11 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
@@ -20685,7 +21117,11 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
@@ -20746,7 +21182,11 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
@@ -20807,7 +21247,11 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
@@ -20868,7 +21312,11 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
@@ -20929,7 +21377,11 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
@@ -20990,7 +21442,11 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr">
         <is>
@@ -21051,7 +21507,11 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
@@ -21112,7 +21572,11 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
@@ -21173,7 +21637,11 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
@@ -21234,7 +21702,11 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
@@ -21295,7 +21767,11 @@
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
@@ -21356,7 +21832,11 @@
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
@@ -21417,7 +21897,11 @@
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
@@ -21478,7 +21962,11 @@
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
@@ -21539,7 +22027,11 @@
       <c r="G256" t="inlineStr"/>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
@@ -21600,7 +22092,11 @@
       <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
@@ -21661,7 +22157,11 @@
       <c r="G258" t="inlineStr"/>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
@@ -21722,7 +22222,11 @@
       <c r="G259" t="inlineStr"/>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
@@ -21783,7 +22287,11 @@
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
@@ -21844,7 +22352,11 @@
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
@@ -21905,7 +22417,11 @@
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
@@ -21966,7 +22482,11 @@
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
@@ -22027,7 +22547,11 @@
       <c r="G264" t="inlineStr"/>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
@@ -22088,7 +22612,11 @@
       <c r="G265" t="inlineStr"/>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr">
         <is>
@@ -22149,7 +22677,11 @@
       <c r="G266" t="inlineStr"/>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr">
         <is>
@@ -22210,7 +22742,11 @@
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
@@ -22271,7 +22807,11 @@
       <c r="G268" t="inlineStr"/>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
@@ -22344,7 +22884,11 @@
       <c r="G269" t="inlineStr"/>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
@@ -22405,7 +22949,11 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr">
         <is>
@@ -22466,7 +23014,11 @@
       <c r="G271" t="inlineStr"/>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr">
         <is>
@@ -22527,7 +23079,11 @@
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr">
         <is>
@@ -22588,7 +23144,11 @@
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
@@ -22649,7 +23209,11 @@
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr">
         <is>
@@ -22710,7 +23274,11 @@
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
@@ -22771,7 +23339,11 @@
       <c r="G276" t="inlineStr"/>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
@@ -22832,7 +23404,11 @@
       <c r="G277" t="inlineStr"/>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
@@ -22893,7 +23469,11 @@
       <c r="G278" t="inlineStr"/>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
@@ -22954,7 +23534,11 @@
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
@@ -23015,7 +23599,11 @@
       <c r="G280" t="inlineStr"/>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
@@ -23076,7 +23664,11 @@
       <c r="G281" t="inlineStr"/>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr">
         <is>
@@ -23137,7 +23729,11 @@
       <c r="G282" t="inlineStr"/>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
@@ -23198,7 +23794,11 @@
       <c r="G283" t="inlineStr"/>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
@@ -23259,7 +23859,11 @@
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr">
         <is>
@@ -23320,7 +23924,11 @@
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
@@ -23381,7 +23989,11 @@
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
@@ -23442,7 +24054,11 @@
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr">
         <is>
@@ -23519,7 +24135,11 @@
       </c>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
@@ -23580,7 +24200,11 @@
       <c r="G289" t="inlineStr"/>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
@@ -23641,7 +24265,11 @@
       <c r="G290" t="inlineStr"/>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr">
         <is>
@@ -23702,7 +24330,11 @@
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
@@ -23763,7 +24395,11 @@
       <c r="G292" t="inlineStr"/>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr">
         <is>
@@ -23824,7 +24460,11 @@
       <c r="G293" t="inlineStr"/>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
@@ -23901,7 +24541,11 @@
       </c>
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr">
         <is>
@@ -23962,7 +24606,11 @@
       <c r="G295" t="inlineStr"/>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
@@ -24023,7 +24671,11 @@
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
@@ -24084,7 +24736,11 @@
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
@@ -24145,7 +24801,11 @@
       <c r="G298" t="inlineStr"/>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr"/>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
@@ -24206,7 +24866,11 @@
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
@@ -24267,7 +24931,11 @@
       <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
@@ -24332,7 +25000,11 @@
       <c r="G301" t="inlineStr"/>
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr"/>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr">
         <is>
@@ -24401,7 +25073,11 @@
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
@@ -24462,7 +25138,11 @@
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
@@ -24523,7 +25203,11 @@
       <c r="G304" t="inlineStr"/>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr">
         <is>
@@ -24584,7 +25268,11 @@
       <c r="G305" t="inlineStr"/>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
@@ -24645,7 +25333,11 @@
       <c r="G306" t="inlineStr"/>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K306" t="inlineStr"/>
       <c r="L306" t="inlineStr">
         <is>
@@ -24706,7 +25398,11 @@
       <c r="G307" t="inlineStr"/>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
@@ -24775,7 +25471,11 @@
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
@@ -24836,7 +25536,11 @@
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
@@ -24897,7 +25601,11 @@
       <c r="G310" t="inlineStr"/>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
-      <c r="J310" t="inlineStr"/>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr">
         <is>
@@ -24958,7 +25666,11 @@
       <c r="G311" t="inlineStr"/>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
@@ -25019,7 +25731,11 @@
       <c r="G312" t="inlineStr"/>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
@@ -25080,7 +25796,11 @@
       <c r="G313" t="inlineStr"/>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
@@ -25141,7 +25861,11 @@
       <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr">
         <is>
@@ -25202,7 +25926,11 @@
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
@@ -25263,7 +25991,11 @@
       <c r="G316" t="inlineStr"/>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
@@ -25324,7 +26056,11 @@
       <c r="G317" t="inlineStr"/>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
-      <c r="J317" t="inlineStr"/>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
@@ -25385,7 +26121,11 @@
       <c r="G318" t="inlineStr"/>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr"/>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr">
         <is>
@@ -25446,7 +26186,11 @@
       <c r="G319" t="inlineStr"/>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
@@ -25507,7 +26251,11 @@
       <c r="G320" t="inlineStr"/>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr">
         <is>
@@ -25568,7 +26316,11 @@
       <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
@@ -25629,7 +26381,11 @@
       <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
@@ -25690,7 +26446,11 @@
       <c r="G323" t="inlineStr"/>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
@@ -25751,7 +26511,11 @@
       <c r="G324" t="inlineStr"/>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
@@ -25812,7 +26576,11 @@
       <c r="G325" t="inlineStr"/>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
@@ -25873,7 +26641,11 @@
       <c r="G326" t="inlineStr"/>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
@@ -25934,7 +26706,11 @@
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr">
         <is>
@@ -25995,7 +26771,11 @@
       <c r="G328" t="inlineStr"/>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
@@ -26056,7 +26836,11 @@
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
@@ -26117,7 +26901,11 @@
       <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
@@ -26178,7 +26966,11 @@
       <c r="G331" t="inlineStr"/>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
@@ -26239,7 +27031,11 @@
       <c r="G332" t="inlineStr"/>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
@@ -26300,7 +27096,11 @@
       <c r="G333" t="inlineStr"/>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
@@ -26361,7 +27161,11 @@
       <c r="G334" t="inlineStr"/>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
@@ -26422,7 +27226,11 @@
       <c r="G335" t="inlineStr"/>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
@@ -26483,7 +27291,11 @@
       <c r="G336" t="inlineStr"/>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr"/>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr">
         <is>
@@ -26544,7 +27356,11 @@
       <c r="G337" t="inlineStr"/>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
@@ -26605,7 +27421,11 @@
       <c r="G338" t="inlineStr"/>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
@@ -26666,7 +27486,11 @@
       <c r="G339" t="inlineStr"/>
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr">
         <is>
@@ -26727,7 +27551,11 @@
       <c r="G340" t="inlineStr"/>
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
@@ -26788,7 +27616,11 @@
       <c r="G341" t="inlineStr"/>
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
@@ -26849,7 +27681,11 @@
       <c r="G342" t="inlineStr"/>
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
@@ -26910,7 +27746,11 @@
       <c r="G343" t="inlineStr"/>
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
@@ -26971,7 +27811,11 @@
       <c r="G344" t="inlineStr"/>
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
@@ -27032,7 +27876,11 @@
       <c r="G345" t="inlineStr"/>
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
-      <c r="J345" t="inlineStr"/>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
@@ -27093,7 +27941,11 @@
       <c r="G346" t="inlineStr"/>
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
-      <c r="J346" t="inlineStr"/>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
@@ -27154,7 +28006,11 @@
       <c r="G347" t="inlineStr"/>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
@@ -27215,7 +28071,11 @@
       <c r="G348" t="inlineStr"/>
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
@@ -27276,7 +28136,11 @@
       <c r="G349" t="inlineStr"/>
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
@@ -27337,7 +28201,11 @@
       <c r="G350" t="inlineStr"/>
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
@@ -27398,7 +28266,11 @@
       <c r="G351" t="inlineStr"/>
       <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
@@ -27459,7 +28331,11 @@
       <c r="G352" t="inlineStr"/>
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
@@ -27520,7 +28396,11 @@
       <c r="G353" t="inlineStr"/>
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
@@ -27581,7 +28461,11 @@
       <c r="G354" t="inlineStr"/>
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr"/>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr">
         <is>
@@ -27654,7 +28538,11 @@
       </c>
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
@@ -27715,7 +28603,11 @@
       <c r="G356" t="inlineStr"/>
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
@@ -27776,7 +28668,11 @@
       <c r="G357" t="inlineStr"/>
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
-      <c r="J357" t="inlineStr"/>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
@@ -27837,7 +28733,11 @@
       <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
@@ -27898,7 +28798,11 @@
       <c r="G359" t="inlineStr"/>
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr">
         <is>
@@ -27959,7 +28863,11 @@
       <c r="G360" t="inlineStr"/>
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
@@ -28020,7 +28928,11 @@
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr">
         <is>
@@ -28081,7 +28993,11 @@
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
@@ -28158,7 +29074,11 @@
       </c>
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
-      <c r="J363" t="inlineStr"/>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr">
         <is>
@@ -28219,7 +29139,11 @@
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
@@ -28280,7 +29204,11 @@
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
@@ -28341,7 +29269,11 @@
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
@@ -28402,7 +29334,11 @@
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
@@ -28463,7 +29399,11 @@
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
@@ -28524,7 +29464,11 @@
       <c r="G369" t="inlineStr"/>
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
@@ -28585,7 +29529,11 @@
       <c r="G370" t="inlineStr"/>
       <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr"/>
-      <c r="J370" t="inlineStr"/>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
@@ -28646,7 +29594,11 @@
       <c r="G371" t="inlineStr"/>
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
-      <c r="J371" t="inlineStr"/>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
@@ -28707,7 +29659,11 @@
       <c r="G372" t="inlineStr"/>
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr"/>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
@@ -28768,7 +29724,11 @@
       <c r="G373" t="inlineStr"/>
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
-      <c r="J373" t="inlineStr"/>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr">
         <is>
@@ -28829,7 +29789,11 @@
       <c r="G374" t="inlineStr"/>
       <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr"/>
-      <c r="J374" t="inlineStr"/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
@@ -28890,7 +29854,11 @@
       <c r="G375" t="inlineStr"/>
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
-      <c r="J375" t="inlineStr"/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr">
         <is>
@@ -28951,7 +29919,11 @@
       <c r="G376" t="inlineStr"/>
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
-      <c r="J376" t="inlineStr"/>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
@@ -29012,7 +29984,11 @@
       <c r="G377" t="inlineStr"/>
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
-      <c r="J377" t="inlineStr"/>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
@@ -29073,7 +30049,11 @@
       <c r="G378" t="inlineStr"/>
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
-      <c r="J378" t="inlineStr"/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
@@ -29134,7 +30114,11 @@
       <c r="G379" t="inlineStr"/>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
-      <c r="J379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
@@ -29195,7 +30179,11 @@
       <c r="G380" t="inlineStr"/>
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
-      <c r="J380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
@@ -29256,7 +30244,11 @@
       <c r="G381" t="inlineStr"/>
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
-      <c r="J381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
@@ -29317,7 +30309,11 @@
       <c r="G382" t="inlineStr"/>
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
-      <c r="J382" t="inlineStr"/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
@@ -29378,7 +30374,11 @@
       <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
-      <c r="J383" t="inlineStr"/>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr">
         <is>
@@ -29439,7 +30439,11 @@
       <c r="G384" t="inlineStr"/>
       <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
@@ -29500,7 +30504,11 @@
       <c r="G385" t="inlineStr"/>
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr">
         <is>
@@ -29561,7 +30569,11 @@
       <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
-      <c r="J386" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
@@ -29622,7 +30634,11 @@
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
-      <c r="J387" t="inlineStr"/>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
@@ -29683,7 +30699,11 @@
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
-      <c r="J388" t="inlineStr"/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
@@ -29744,7 +30764,11 @@
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr">
         <is>
@@ -29805,7 +30829,11 @@
       <c r="G390" t="inlineStr"/>
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr"/>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
@@ -29866,7 +30894,11 @@
       <c r="G391" t="inlineStr"/>
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
-      <c r="J391" t="inlineStr"/>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
@@ -29927,7 +30959,11 @@
       <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
-      <c r="J392" t="inlineStr"/>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr">
         <is>
@@ -29988,7 +31024,11 @@
       <c r="G393" t="inlineStr"/>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr"/>
-      <c r="J393" t="inlineStr"/>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
@@ -30049,7 +31089,11 @@
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr">
         <is>
@@ -30110,7 +31154,11 @@
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr"/>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
@@ -30171,7 +31219,11 @@
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
@@ -30232,7 +31284,11 @@
       <c r="G397" t="inlineStr"/>
       <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr">
         <is>
@@ -30293,7 +31349,11 @@
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
-      <c r="J398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
@@ -30354,7 +31414,11 @@
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
@@ -30415,7 +31479,11 @@
       <c r="G400" t="inlineStr"/>
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr"/>
-      <c r="J400" t="inlineStr"/>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
@@ -30492,7 +31560,11 @@
       </c>
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr"/>
-      <c r="J401" t="inlineStr"/>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr">
         <is>
@@ -30553,7 +31625,11 @@
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr"/>
-      <c r="J402" t="inlineStr"/>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
@@ -30614,7 +31690,11 @@
       <c r="G403" t="inlineStr"/>
       <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
-      <c r="J403" t="inlineStr"/>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
@@ -30675,7 +31755,11 @@
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr">
         <is>
@@ -30736,7 +31820,11 @@
       <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr"/>
-      <c r="J405" t="inlineStr"/>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr">
         <is>
@@ -30797,7 +31885,11 @@
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr"/>
-      <c r="J406" t="inlineStr"/>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr">
         <is>
@@ -30858,7 +31950,11 @@
       <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr"/>
-      <c r="J407" t="inlineStr"/>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr">
         <is>
@@ -30919,7 +32015,11 @@
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr"/>
-      <c r="J408" t="inlineStr"/>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr">
         <is>
@@ -30980,7 +32080,11 @@
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
@@ -31041,7 +32145,11 @@
       <c r="G410" t="inlineStr"/>
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
-      <c r="J410" t="inlineStr"/>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
@@ -31102,7 +32210,11 @@
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
@@ -31163,7 +32275,11 @@
       <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr"/>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr">
         <is>
@@ -31224,7 +32340,11 @@
       <c r="G413" t="inlineStr"/>
       <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr"/>
-      <c r="J413" t="inlineStr"/>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr">
         <is>
@@ -31285,7 +32405,11 @@
       <c r="G414" t="inlineStr"/>
       <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr"/>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr">
         <is>
@@ -31346,7 +32470,11 @@
       <c r="G415" t="inlineStr"/>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
@@ -31407,7 +32535,11 @@
       <c r="G416" t="inlineStr"/>
       <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr"/>
-      <c r="J416" t="inlineStr"/>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
@@ -31468,7 +32600,11 @@
       <c r="G417" t="inlineStr"/>
       <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
@@ -31529,7 +32665,11 @@
       <c r="G418" t="inlineStr"/>
       <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr">
         <is>
@@ -31590,7 +32730,11 @@
       <c r="G419" t="inlineStr"/>
       <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr"/>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr">
         <is>
@@ -31663,7 +32807,11 @@
       </c>
       <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr"/>
-      <c r="J420" t="inlineStr"/>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr">
         <is>
@@ -31724,7 +32872,11 @@
       <c r="G421" t="inlineStr"/>
       <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr"/>
-      <c r="J421" t="inlineStr"/>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr">
         <is>
@@ -31785,7 +32937,11 @@
       <c r="G422" t="inlineStr"/>
       <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr"/>
-      <c r="J422" t="inlineStr"/>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr">
         <is>
@@ -31846,7 +33002,11 @@
       <c r="G423" t="inlineStr"/>
       <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr"/>
-      <c r="J423" t="inlineStr"/>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr">
         <is>
@@ -31907,7 +33067,11 @@
       <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr"/>
-      <c r="J424" t="inlineStr"/>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr">
         <is>
@@ -31968,7 +33132,11 @@
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr"/>
-      <c r="J425" t="inlineStr"/>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
@@ -32029,7 +33197,11 @@
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr"/>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
@@ -32090,7 +33262,11 @@
       <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr"/>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
@@ -32151,7 +33327,11 @@
       <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr"/>
-      <c r="J428" t="inlineStr"/>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
@@ -32212,7 +33392,11 @@
       <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr"/>
-      <c r="J429" t="inlineStr"/>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr">
         <is>
@@ -32273,7 +33457,11 @@
       <c r="G430" t="inlineStr"/>
       <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr"/>
-      <c r="J430" t="inlineStr"/>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
@@ -32334,7 +33522,11 @@
       <c r="G431" t="inlineStr"/>
       <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr">
         <is>
@@ -32411,7 +33603,11 @@
       </c>
       <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr"/>
-      <c r="J432" t="inlineStr"/>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr">
         <is>
@@ -32472,7 +33668,11 @@
       <c r="G433" t="inlineStr"/>
       <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr"/>
-      <c r="J433" t="inlineStr"/>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr">
         <is>
@@ -32549,7 +33749,11 @@
       </c>
       <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr"/>
-      <c r="J434" t="inlineStr"/>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr">
         <is>
@@ -32622,7 +33826,11 @@
       </c>
       <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr"/>
-      <c r="J435" t="inlineStr"/>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr">
         <is>
@@ -32699,7 +33907,11 @@
       </c>
       <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr"/>
-      <c r="J436" t="inlineStr"/>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr">
         <is>
@@ -32772,7 +33984,11 @@
       <c r="G437" t="inlineStr"/>
       <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr"/>
-      <c r="J437" t="inlineStr"/>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr">
         <is>
@@ -32833,7 +34049,11 @@
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr"/>
-      <c r="J438" t="inlineStr"/>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr">
         <is>
@@ -32894,7 +34114,11 @@
       <c r="G439" t="inlineStr"/>
       <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr">
         <is>
@@ -32971,7 +34195,11 @@
       </c>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr">
         <is>
@@ -33032,7 +34260,11 @@
       <c r="G441" t="inlineStr"/>
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr">
         <is>
@@ -33093,7 +34325,11 @@
       <c r="G442" t="inlineStr"/>
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr">
         <is>
@@ -33154,7 +34390,11 @@
       <c r="G443" t="inlineStr"/>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
-      <c r="J443" t="inlineStr"/>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr">
         <is>
@@ -33215,7 +34455,11 @@
       <c r="G444" t="inlineStr"/>
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr">
         <is>
@@ -33276,7 +34520,11 @@
       <c r="G445" t="inlineStr"/>
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr">
         <is>
@@ -33337,7 +34585,11 @@
       <c r="G446" t="inlineStr"/>
       <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr"/>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr">
         <is>
@@ -33398,7 +34650,11 @@
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr">
         <is>
@@ -33459,7 +34715,11 @@
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr"/>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr">
         <is>
@@ -33520,7 +34780,11 @@
       <c r="G449" t="inlineStr"/>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr">
         <is>
@@ -33581,7 +34845,11 @@
       <c r="G450" t="inlineStr"/>
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr">
         <is>
@@ -33654,7 +34922,11 @@
       </c>
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
-      <c r="J451" t="inlineStr"/>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr">
         <is>
@@ -33715,7 +34987,11 @@
       <c r="G452" t="inlineStr"/>
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr"/>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr">
         <is>
@@ -33776,7 +35052,11 @@
       <c r="G453" t="inlineStr"/>
       <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr"/>
-      <c r="J453" t="inlineStr"/>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr">
         <is>
@@ -33837,7 +35117,11 @@
       <c r="G454" t="inlineStr"/>
       <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr">
         <is>
@@ -33898,7 +35182,11 @@
       <c r="G455" t="inlineStr"/>
       <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
-      <c r="J455" t="inlineStr"/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr">
         <is>
@@ -33959,7 +35247,11 @@
       <c r="G456" t="inlineStr"/>
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr">
         <is>
@@ -34020,7 +35312,11 @@
       <c r="G457" t="inlineStr"/>
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
-      <c r="J457" t="inlineStr"/>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr">
         <is>
@@ -34081,7 +35377,11 @@
       <c r="G458" t="inlineStr"/>
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr">
         <is>
@@ -34142,7 +35442,11 @@
       <c r="G459" t="inlineStr"/>
       <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K459" t="inlineStr"/>
       <c r="L459" t="inlineStr">
         <is>
@@ -34203,7 +35507,11 @@
       <c r="G460" t="inlineStr"/>
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr">
         <is>
@@ -34264,7 +35572,11 @@
       <c r="G461" t="inlineStr"/>
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr">
         <is>
@@ -34325,7 +35637,11 @@
       <c r="G462" t="inlineStr"/>
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr">
         <is>
@@ -34386,7 +35702,11 @@
       <c r="G463" t="inlineStr"/>
       <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr">
         <is>
@@ -34447,7 +35767,11 @@
       <c r="G464" t="inlineStr"/>
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr">
         <is>
@@ -34508,7 +35832,11 @@
       <c r="G465" t="inlineStr"/>
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr">
         <is>
@@ -34569,7 +35897,11 @@
       <c r="G466" t="inlineStr"/>
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr">
         <is>
@@ -34630,7 +35962,11 @@
       <c r="G467" t="inlineStr"/>
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr"/>
-      <c r="J467" t="inlineStr"/>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr">
         <is>
@@ -34691,7 +36027,11 @@
       <c r="G468" t="inlineStr"/>
       <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
-      <c r="J468" t="inlineStr"/>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr">
         <is>
@@ -34752,7 +36092,11 @@
       <c r="G469" t="inlineStr"/>
       <c r="H469" t="inlineStr"/>
       <c r="I469" t="inlineStr"/>
-      <c r="J469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr">
         <is>
@@ -34813,7 +36157,11 @@
       <c r="G470" t="inlineStr"/>
       <c r="H470" t="inlineStr"/>
       <c r="I470" t="inlineStr"/>
-      <c r="J470" t="inlineStr"/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr">
         <is>
@@ -34874,7 +36222,11 @@
       <c r="G471" t="inlineStr"/>
       <c r="H471" t="inlineStr"/>
       <c r="I471" t="inlineStr"/>
-      <c r="J471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr">
         <is>
@@ -34935,7 +36287,11 @@
       <c r="G472" t="inlineStr"/>
       <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr"/>
-      <c r="J472" t="inlineStr"/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr">
         <is>
@@ -34996,7 +36352,11 @@
       <c r="G473" t="inlineStr"/>
       <c r="H473" t="inlineStr"/>
       <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
@@ -35057,7 +36417,11 @@
       <c r="G474" t="inlineStr"/>
       <c r="H474" t="inlineStr"/>
       <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr">
         <is>
@@ -35118,7 +36482,11 @@
       <c r="G475" t="inlineStr"/>
       <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr">
         <is>
@@ -35179,7 +36547,11 @@
       <c r="G476" t="inlineStr"/>
       <c r="H476" t="inlineStr"/>
       <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr">
         <is>
@@ -35240,7 +36612,11 @@
       <c r="G477" t="inlineStr"/>
       <c r="H477" t="inlineStr"/>
       <c r="I477" t="inlineStr"/>
-      <c r="J477" t="inlineStr"/>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr">
         <is>
@@ -35301,7 +36677,11 @@
       <c r="G478" t="inlineStr"/>
       <c r="H478" t="inlineStr"/>
       <c r="I478" t="inlineStr"/>
-      <c r="J478" t="inlineStr"/>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr">
         <is>
@@ -35362,7 +36742,11 @@
       <c r="G479" t="inlineStr"/>
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr">
         <is>
@@ -35423,7 +36807,11 @@
       <c r="G480" t="inlineStr"/>
       <c r="H480" t="inlineStr"/>
       <c r="I480" t="inlineStr"/>
-      <c r="J480" t="inlineStr"/>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr">
         <is>
@@ -35484,7 +36872,11 @@
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr"/>
       <c r="I481" t="inlineStr"/>
-      <c r="J481" t="inlineStr"/>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr">
         <is>
@@ -35545,7 +36937,11 @@
       <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr"/>
       <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr">
         <is>
@@ -35606,7 +37002,11 @@
       <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr">
         <is>
@@ -35667,7 +37067,11 @@
       <c r="G484" t="inlineStr"/>
       <c r="H484" t="inlineStr"/>
       <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr">
         <is>
@@ -35736,7 +37140,11 @@
       </c>
       <c r="H485" t="inlineStr"/>
       <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr">
         <is>
@@ -35797,7 +37205,11 @@
       <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr">
         <is>
@@ -35858,7 +37270,11 @@
       <c r="G487" t="inlineStr"/>
       <c r="H487" t="inlineStr"/>
       <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr">
         <is>
@@ -35919,7 +37335,11 @@
       <c r="G488" t="inlineStr"/>
       <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr"/>
-      <c r="J488" t="inlineStr"/>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr">
         <is>
@@ -35980,7 +37400,11 @@
       <c r="G489" t="inlineStr"/>
       <c r="H489" t="inlineStr"/>
       <c r="I489" t="inlineStr"/>
-      <c r="J489" t="inlineStr"/>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
@@ -36041,7 +37465,11 @@
       <c r="G490" t="inlineStr"/>
       <c r="H490" t="inlineStr"/>
       <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr"/>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr">
         <is>
@@ -36102,7 +37530,11 @@
       <c r="G491" t="inlineStr"/>
       <c r="H491" t="inlineStr"/>
       <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr"/>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr">
         <is>
@@ -36163,7 +37595,11 @@
       <c r="G492" t="inlineStr"/>
       <c r="H492" t="inlineStr"/>
       <c r="I492" t="inlineStr"/>
-      <c r="J492" t="inlineStr"/>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr">
         <is>
@@ -36224,7 +37660,11 @@
       <c r="G493" t="inlineStr"/>
       <c r="H493" t="inlineStr"/>
       <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr">
         <is>
@@ -36285,7 +37725,11 @@
       <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
       <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr">
         <is>
@@ -36346,7 +37790,11 @@
       <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="inlineStr"/>
-      <c r="J495" t="inlineStr"/>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr">
         <is>
@@ -36407,7 +37855,11 @@
       <c r="G496" t="inlineStr"/>
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="inlineStr"/>
-      <c r="J496" t="inlineStr"/>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr">
         <is>
@@ -36468,7 +37920,11 @@
       <c r="G497" t="inlineStr"/>
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr"/>
-      <c r="J497" t="inlineStr"/>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr">
         <is>
@@ -36529,7 +37985,11 @@
       <c r="G498" t="inlineStr"/>
       <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr"/>
-      <c r="J498" t="inlineStr"/>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K498" t="inlineStr"/>
       <c r="L498" t="inlineStr">
         <is>
@@ -36590,7 +38050,11 @@
       <c r="G499" t="inlineStr"/>
       <c r="H499" t="inlineStr"/>
       <c r="I499" t="inlineStr"/>
-      <c r="J499" t="inlineStr"/>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr">
         <is>
@@ -36651,7 +38115,11 @@
       <c r="G500" t="inlineStr"/>
       <c r="H500" t="inlineStr"/>
       <c r="I500" t="inlineStr"/>
-      <c r="J500" t="inlineStr"/>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr">
         <is>
@@ -36712,7 +38180,11 @@
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="inlineStr"/>
-      <c r="J501" t="inlineStr"/>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
@@ -36785,7 +38257,11 @@
       </c>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr">
         <is>
@@ -36846,7 +38322,11 @@
       <c r="G503" t="inlineStr"/>
       <c r="H503" t="inlineStr"/>
       <c r="I503" t="inlineStr"/>
-      <c r="J503" t="inlineStr"/>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr">
         <is>
@@ -36907,7 +38387,11 @@
       <c r="G504" t="inlineStr"/>
       <c r="H504" t="inlineStr"/>
       <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr"/>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr">
         <is>
@@ -36968,7 +38452,11 @@
       <c r="G505" t="inlineStr"/>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="inlineStr"/>
-      <c r="J505" t="inlineStr"/>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr">
         <is>
@@ -37029,7 +38517,11 @@
       <c r="G506" t="inlineStr"/>
       <c r="H506" t="inlineStr"/>
       <c r="I506" t="inlineStr"/>
-      <c r="J506" t="inlineStr"/>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr">
         <is>
@@ -37090,7 +38582,11 @@
       <c r="G507" t="inlineStr"/>
       <c r="H507" t="inlineStr"/>
       <c r="I507" t="inlineStr"/>
-      <c r="J507" t="inlineStr"/>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr">
         <is>
@@ -37151,7 +38647,11 @@
       <c r="G508" t="inlineStr"/>
       <c r="H508" t="inlineStr"/>
       <c r="I508" t="inlineStr"/>
-      <c r="J508" t="inlineStr"/>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr">
         <is>
@@ -37212,7 +38712,11 @@
       <c r="G509" t="inlineStr"/>
       <c r="H509" t="inlineStr"/>
       <c r="I509" t="inlineStr"/>
-      <c r="J509" t="inlineStr"/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr">
         <is>
@@ -37273,7 +38777,11 @@
       <c r="G510" t="inlineStr"/>
       <c r="H510" t="inlineStr"/>
       <c r="I510" t="inlineStr"/>
-      <c r="J510" t="inlineStr"/>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr">
         <is>
@@ -37334,7 +38842,11 @@
       <c r="G511" t="inlineStr"/>
       <c r="H511" t="inlineStr"/>
       <c r="I511" t="inlineStr"/>
-      <c r="J511" t="inlineStr"/>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr">
         <is>
@@ -37395,7 +38907,11 @@
       <c r="G512" t="inlineStr"/>
       <c r="H512" t="inlineStr"/>
       <c r="I512" t="inlineStr"/>
-      <c r="J512" t="inlineStr"/>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K512" t="inlineStr"/>
       <c r="L512" t="inlineStr">
         <is>
@@ -37456,7 +38972,11 @@
       <c r="G513" t="inlineStr"/>
       <c r="H513" t="inlineStr"/>
       <c r="I513" t="inlineStr"/>
-      <c r="J513" t="inlineStr"/>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr">
         <is>
@@ -37517,7 +39037,11 @@
       <c r="G514" t="inlineStr"/>
       <c r="H514" t="inlineStr"/>
       <c r="I514" t="inlineStr"/>
-      <c r="J514" t="inlineStr"/>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr">
         <is>
@@ -37578,7 +39102,11 @@
       <c r="G515" t="inlineStr"/>
       <c r="H515" t="inlineStr"/>
       <c r="I515" t="inlineStr"/>
-      <c r="J515" t="inlineStr"/>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr">
         <is>
@@ -37639,7 +39167,11 @@
       <c r="G516" t="inlineStr"/>
       <c r="H516" t="inlineStr"/>
       <c r="I516" t="inlineStr"/>
-      <c r="J516" t="inlineStr"/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
@@ -37700,7 +39232,11 @@
       <c r="G517" t="inlineStr"/>
       <c r="H517" t="inlineStr"/>
       <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr"/>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
@@ -37761,7 +39297,11 @@
       <c r="G518" t="inlineStr"/>
       <c r="H518" t="inlineStr"/>
       <c r="I518" t="inlineStr"/>
-      <c r="J518" t="inlineStr"/>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr">
         <is>
@@ -37822,7 +39362,11 @@
       <c r="G519" t="inlineStr"/>
       <c r="H519" t="inlineStr"/>
       <c r="I519" t="inlineStr"/>
-      <c r="J519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K519" t="inlineStr"/>
       <c r="L519" t="inlineStr">
         <is>
@@ -37883,7 +39427,11 @@
       <c r="G520" t="inlineStr"/>
       <c r="H520" t="inlineStr"/>
       <c r="I520" t="inlineStr"/>
-      <c r="J520" t="inlineStr"/>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr">
         <is>
@@ -37944,7 +39492,11 @@
       <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr"/>
-      <c r="J521" t="inlineStr"/>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr">
         <is>
@@ -38005,7 +39557,11 @@
       <c r="G522" t="inlineStr"/>
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="inlineStr"/>
-      <c r="J522" t="inlineStr"/>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr">
         <is>
@@ -38066,7 +39622,11 @@
       <c r="G523" t="inlineStr"/>
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="inlineStr"/>
-      <c r="J523" t="inlineStr"/>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr">
         <is>
@@ -38127,7 +39687,11 @@
       <c r="G524" t="inlineStr"/>
       <c r="H524" t="inlineStr"/>
       <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr">
         <is>
@@ -38188,7 +39752,11 @@
       <c r="G525" t="inlineStr"/>
       <c r="H525" t="inlineStr"/>
       <c r="I525" t="inlineStr"/>
-      <c r="J525" t="inlineStr"/>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr">
         <is>
@@ -38249,7 +39817,11 @@
       <c r="G526" t="inlineStr"/>
       <c r="H526" t="inlineStr"/>
       <c r="I526" t="inlineStr"/>
-      <c r="J526" t="inlineStr"/>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr">
         <is>
@@ -38310,7 +39882,11 @@
       <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr"/>
       <c r="I527" t="inlineStr"/>
-      <c r="J527" t="inlineStr"/>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr">
         <is>
@@ -38371,7 +39947,11 @@
       <c r="G528" t="inlineStr"/>
       <c r="H528" t="inlineStr"/>
       <c r="I528" t="inlineStr"/>
-      <c r="J528" t="inlineStr"/>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr">
         <is>
@@ -38432,7 +40012,11 @@
       <c r="G529" t="inlineStr"/>
       <c r="H529" t="inlineStr"/>
       <c r="I529" t="inlineStr"/>
-      <c r="J529" t="inlineStr"/>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr">
         <is>
@@ -38493,7 +40077,11 @@
       <c r="G530" t="inlineStr"/>
       <c r="H530" t="inlineStr"/>
       <c r="I530" t="inlineStr"/>
-      <c r="J530" t="inlineStr"/>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K530" t="inlineStr"/>
       <c r="L530" t="inlineStr">
         <is>
@@ -38554,7 +40142,11 @@
       <c r="G531" t="inlineStr"/>
       <c r="H531" t="inlineStr"/>
       <c r="I531" t="inlineStr"/>
-      <c r="J531" t="inlineStr"/>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K531" t="inlineStr"/>
       <c r="L531" t="inlineStr">
         <is>
@@ -38615,7 +40207,11 @@
       <c r="G532" t="inlineStr"/>
       <c r="H532" t="inlineStr"/>
       <c r="I532" t="inlineStr"/>
-      <c r="J532" t="inlineStr"/>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K532" t="inlineStr"/>
       <c r="L532" t="inlineStr">
         <is>
@@ -38688,7 +40284,11 @@
       </c>
       <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr"/>
-      <c r="J533" t="inlineStr"/>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr">
         <is>
@@ -38749,7 +40349,11 @@
       <c r="G534" t="inlineStr"/>
       <c r="H534" t="inlineStr"/>
       <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr"/>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K534" t="inlineStr"/>
       <c r="L534" t="inlineStr">
         <is>
@@ -38810,7 +40414,11 @@
       <c r="G535" t="inlineStr"/>
       <c r="H535" t="inlineStr"/>
       <c r="I535" t="inlineStr"/>
-      <c r="J535" t="inlineStr"/>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K535" t="inlineStr"/>
       <c r="L535" t="inlineStr">
         <is>
@@ -38871,7 +40479,11 @@
       <c r="G536" t="inlineStr"/>
       <c r="H536" t="inlineStr"/>
       <c r="I536" t="inlineStr"/>
-      <c r="J536" t="inlineStr"/>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K536" t="inlineStr"/>
       <c r="L536" t="inlineStr">
         <is>
@@ -38932,7 +40544,11 @@
       <c r="G537" t="inlineStr"/>
       <c r="H537" t="inlineStr"/>
       <c r="I537" t="inlineStr"/>
-      <c r="J537" t="inlineStr"/>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K537" t="inlineStr"/>
       <c r="L537" t="inlineStr">
         <is>
@@ -38993,7 +40609,11 @@
       <c r="G538" t="inlineStr"/>
       <c r="H538" t="inlineStr"/>
       <c r="I538" t="inlineStr"/>
-      <c r="J538" t="inlineStr"/>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K538" t="inlineStr"/>
       <c r="L538" t="inlineStr">
         <is>
@@ -39054,7 +40674,11 @@
       <c r="G539" t="inlineStr"/>
       <c r="H539" t="inlineStr"/>
       <c r="I539" t="inlineStr"/>
-      <c r="J539" t="inlineStr"/>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr">
         <is>
@@ -39115,7 +40739,11 @@
       <c r="G540" t="inlineStr"/>
       <c r="H540" t="inlineStr"/>
       <c r="I540" t="inlineStr"/>
-      <c r="J540" t="inlineStr"/>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr">
         <is>
@@ -39176,7 +40804,11 @@
       <c r="G541" t="inlineStr"/>
       <c r="H541" t="inlineStr"/>
       <c r="I541" t="inlineStr"/>
-      <c r="J541" t="inlineStr"/>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K541" t="inlineStr"/>
       <c r="L541" t="inlineStr">
         <is>
@@ -39237,7 +40869,11 @@
       <c r="G542" t="inlineStr"/>
       <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr"/>
-      <c r="J542" t="inlineStr"/>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr">
         <is>
@@ -39298,7 +40934,11 @@
       <c r="G543" t="inlineStr"/>
       <c r="H543" t="inlineStr"/>
       <c r="I543" t="inlineStr"/>
-      <c r="J543" t="inlineStr"/>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K543" t="inlineStr"/>
       <c r="L543" t="inlineStr">
         <is>
@@ -39359,7 +40999,11 @@
       <c r="G544" t="inlineStr"/>
       <c r="H544" t="inlineStr"/>
       <c r="I544" t="inlineStr"/>
-      <c r="J544" t="inlineStr"/>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr">
         <is>
@@ -39436,7 +41080,11 @@
       </c>
       <c r="H545" t="inlineStr"/>
       <c r="I545" t="inlineStr"/>
-      <c r="J545" t="inlineStr"/>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K545" t="inlineStr"/>
       <c r="L545" t="inlineStr">
         <is>
@@ -39497,7 +41145,11 @@
       <c r="G546" t="inlineStr"/>
       <c r="H546" t="inlineStr"/>
       <c r="I546" t="inlineStr"/>
-      <c r="J546" t="inlineStr"/>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K546" t="inlineStr"/>
       <c r="L546" t="inlineStr">
         <is>
@@ -39558,7 +41210,11 @@
       <c r="G547" t="inlineStr"/>
       <c r="H547" t="inlineStr"/>
       <c r="I547" t="inlineStr"/>
-      <c r="J547" t="inlineStr"/>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K547" t="inlineStr"/>
       <c r="L547" t="inlineStr">
         <is>
@@ -39619,7 +41275,11 @@
       <c r="G548" t="inlineStr"/>
       <c r="H548" t="inlineStr"/>
       <c r="I548" t="inlineStr"/>
-      <c r="J548" t="inlineStr"/>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K548" t="inlineStr"/>
       <c r="L548" t="inlineStr">
         <is>
@@ -39680,7 +41340,11 @@
       <c r="G549" t="inlineStr"/>
       <c r="H549" t="inlineStr"/>
       <c r="I549" t="inlineStr"/>
-      <c r="J549" t="inlineStr"/>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K549" t="inlineStr"/>
       <c r="L549" t="inlineStr">
         <is>
@@ -39741,7 +41405,11 @@
       <c r="G550" t="inlineStr"/>
       <c r="H550" t="inlineStr"/>
       <c r="I550" t="inlineStr"/>
-      <c r="J550" t="inlineStr"/>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K550" t="inlineStr"/>
       <c r="L550" t="inlineStr">
         <is>
@@ -39802,7 +41470,11 @@
       <c r="G551" t="inlineStr"/>
       <c r="H551" t="inlineStr"/>
       <c r="I551" t="inlineStr"/>
-      <c r="J551" t="inlineStr"/>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K551" t="inlineStr"/>
       <c r="L551" t="inlineStr">
         <is>
@@ -39863,7 +41535,11 @@
       <c r="G552" t="inlineStr"/>
       <c r="H552" t="inlineStr"/>
       <c r="I552" t="inlineStr"/>
-      <c r="J552" t="inlineStr"/>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K552" t="inlineStr"/>
       <c r="L552" t="inlineStr">
         <is>
@@ -39924,7 +41600,11 @@
       <c r="G553" t="inlineStr"/>
       <c r="H553" t="inlineStr"/>
       <c r="I553" t="inlineStr"/>
-      <c r="J553" t="inlineStr"/>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K553" t="inlineStr"/>
       <c r="L553" t="inlineStr">
         <is>
@@ -39985,7 +41665,11 @@
       <c r="G554" t="inlineStr"/>
       <c r="H554" t="inlineStr"/>
       <c r="I554" t="inlineStr"/>
-      <c r="J554" t="inlineStr"/>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K554" t="inlineStr"/>
       <c r="L554" t="inlineStr">
         <is>
@@ -40046,7 +41730,11 @@
       <c r="G555" t="inlineStr"/>
       <c r="H555" t="inlineStr"/>
       <c r="I555" t="inlineStr"/>
-      <c r="J555" t="inlineStr"/>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr">
         <is>
@@ -40107,7 +41795,11 @@
       <c r="G556" t="inlineStr"/>
       <c r="H556" t="inlineStr"/>
       <c r="I556" t="inlineStr"/>
-      <c r="J556" t="inlineStr"/>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K556" t="inlineStr"/>
       <c r="L556" t="inlineStr">
         <is>
@@ -40168,7 +41860,11 @@
       <c r="G557" t="inlineStr"/>
       <c r="H557" t="inlineStr"/>
       <c r="I557" t="inlineStr"/>
-      <c r="J557" t="inlineStr"/>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K557" t="inlineStr"/>
       <c r="L557" t="inlineStr">
         <is>
@@ -40229,7 +41925,11 @@
       <c r="G558" t="inlineStr"/>
       <c r="H558" t="inlineStr"/>
       <c r="I558" t="inlineStr"/>
-      <c r="J558" t="inlineStr"/>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K558" t="inlineStr"/>
       <c r="L558" t="inlineStr">
         <is>
@@ -40290,7 +41990,11 @@
       <c r="G559" t="inlineStr"/>
       <c r="H559" t="inlineStr"/>
       <c r="I559" t="inlineStr"/>
-      <c r="J559" t="inlineStr"/>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K559" t="inlineStr"/>
       <c r="L559" t="inlineStr">
         <is>
@@ -40351,7 +42055,11 @@
       <c r="G560" t="inlineStr"/>
       <c r="H560" t="inlineStr"/>
       <c r="I560" t="inlineStr"/>
-      <c r="J560" t="inlineStr"/>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K560" t="inlineStr"/>
       <c r="L560" t="inlineStr">
         <is>
@@ -40412,7 +42120,11 @@
       <c r="G561" t="inlineStr"/>
       <c r="H561" t="inlineStr"/>
       <c r="I561" t="inlineStr"/>
-      <c r="J561" t="inlineStr"/>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K561" t="inlineStr"/>
       <c r="L561" t="inlineStr">
         <is>
@@ -40473,7 +42185,11 @@
       <c r="G562" t="inlineStr"/>
       <c r="H562" t="inlineStr"/>
       <c r="I562" t="inlineStr"/>
-      <c r="J562" t="inlineStr"/>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K562" t="inlineStr"/>
       <c r="L562" t="inlineStr">
         <is>
@@ -40534,7 +42250,11 @@
       <c r="G563" t="inlineStr"/>
       <c r="H563" t="inlineStr"/>
       <c r="I563" t="inlineStr"/>
-      <c r="J563" t="inlineStr"/>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K563" t="inlineStr"/>
       <c r="L563" t="inlineStr">
         <is>
@@ -40595,7 +42315,11 @@
       <c r="G564" t="inlineStr"/>
       <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr"/>
-      <c r="J564" t="inlineStr"/>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K564" t="inlineStr"/>
       <c r="L564" t="inlineStr">
         <is>
@@ -40656,7 +42380,11 @@
       <c r="G565" t="inlineStr"/>
       <c r="H565" t="inlineStr"/>
       <c r="I565" t="inlineStr"/>
-      <c r="J565" t="inlineStr"/>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr">
         <is>
@@ -40717,7 +42445,11 @@
       <c r="G566" t="inlineStr"/>
       <c r="H566" t="inlineStr"/>
       <c r="I566" t="inlineStr"/>
-      <c r="J566" t="inlineStr"/>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K566" t="inlineStr"/>
       <c r="L566" t="inlineStr">
         <is>
@@ -40778,7 +42510,11 @@
       <c r="G567" t="inlineStr"/>
       <c r="H567" t="inlineStr"/>
       <c r="I567" t="inlineStr"/>
-      <c r="J567" t="inlineStr"/>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K567" t="inlineStr"/>
       <c r="L567" t="inlineStr">
         <is>
@@ -40839,7 +42575,11 @@
       <c r="G568" t="inlineStr"/>
       <c r="H568" t="inlineStr"/>
       <c r="I568" t="inlineStr"/>
-      <c r="J568" t="inlineStr"/>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K568" t="inlineStr"/>
       <c r="L568" t="inlineStr">
         <is>
@@ -40900,7 +42640,11 @@
       <c r="G569" t="inlineStr"/>
       <c r="H569" t="inlineStr"/>
       <c r="I569" t="inlineStr"/>
-      <c r="J569" t="inlineStr"/>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K569" t="inlineStr"/>
       <c r="L569" t="inlineStr">
         <is>
@@ -40961,7 +42705,11 @@
       <c r="G570" t="inlineStr"/>
       <c r="H570" t="inlineStr"/>
       <c r="I570" t="inlineStr"/>
-      <c r="J570" t="inlineStr"/>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr">
         <is>
@@ -41022,7 +42770,11 @@
       <c r="G571" t="inlineStr"/>
       <c r="H571" t="inlineStr"/>
       <c r="I571" t="inlineStr"/>
-      <c r="J571" t="inlineStr"/>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K571" t="inlineStr"/>
       <c r="L571" t="inlineStr">
         <is>
@@ -41083,7 +42835,11 @@
       <c r="G572" t="inlineStr"/>
       <c r="H572" t="inlineStr"/>
       <c r="I572" t="inlineStr"/>
-      <c r="J572" t="inlineStr"/>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K572" t="inlineStr"/>
       <c r="L572" t="inlineStr">
         <is>
@@ -41144,7 +42900,11 @@
       <c r="G573" t="inlineStr"/>
       <c r="H573" t="inlineStr"/>
       <c r="I573" t="inlineStr"/>
-      <c r="J573" t="inlineStr"/>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K573" t="inlineStr"/>
       <c r="L573" t="inlineStr">
         <is>
@@ -41205,7 +42965,11 @@
       <c r="G574" t="inlineStr"/>
       <c r="H574" t="inlineStr"/>
       <c r="I574" t="inlineStr"/>
-      <c r="J574" t="inlineStr"/>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K574" t="inlineStr"/>
       <c r="L574" t="inlineStr">
         <is>
@@ -41266,7 +43030,11 @@
       <c r="G575" t="inlineStr"/>
       <c r="H575" t="inlineStr"/>
       <c r="I575" t="inlineStr"/>
-      <c r="J575" t="inlineStr"/>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr">
         <is>
@@ -41327,7 +43095,11 @@
       <c r="G576" t="inlineStr"/>
       <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr">
         <is>
@@ -41388,7 +43160,11 @@
       <c r="G577" t="inlineStr"/>
       <c r="H577" t="inlineStr"/>
       <c r="I577" t="inlineStr"/>
-      <c r="J577" t="inlineStr"/>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K577" t="inlineStr"/>
       <c r="L577" t="inlineStr">
         <is>
@@ -41449,7 +43225,11 @@
       <c r="G578" t="inlineStr"/>
       <c r="H578" t="inlineStr"/>
       <c r="I578" t="inlineStr"/>
-      <c r="J578" t="inlineStr"/>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr">
         <is>
@@ -41510,7 +43290,11 @@
       <c r="G579" t="inlineStr"/>
       <c r="H579" t="inlineStr"/>
       <c r="I579" t="inlineStr"/>
-      <c r="J579" t="inlineStr"/>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr">
         <is>
@@ -41571,7 +43355,11 @@
       <c r="G580" t="inlineStr"/>
       <c r="H580" t="inlineStr"/>
       <c r="I580" t="inlineStr"/>
-      <c r="J580" t="inlineStr"/>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K580" t="inlineStr"/>
       <c r="L580" t="inlineStr">
         <is>
@@ -41632,7 +43420,11 @@
       <c r="G581" t="inlineStr"/>
       <c r="H581" t="inlineStr"/>
       <c r="I581" t="inlineStr"/>
-      <c r="J581" t="inlineStr"/>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K581" t="inlineStr"/>
       <c r="L581" t="inlineStr">
         <is>
@@ -41693,7 +43485,11 @@
       <c r="G582" t="inlineStr"/>
       <c r="H582" t="inlineStr"/>
       <c r="I582" t="inlineStr"/>
-      <c r="J582" t="inlineStr"/>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K582" t="inlineStr"/>
       <c r="L582" t="inlineStr">
         <is>
@@ -41754,7 +43550,11 @@
       <c r="G583" t="inlineStr"/>
       <c r="H583" t="inlineStr"/>
       <c r="I583" t="inlineStr"/>
-      <c r="J583" t="inlineStr"/>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K583" t="inlineStr"/>
       <c r="L583" t="inlineStr">
         <is>
@@ -41815,7 +43615,11 @@
       <c r="G584" t="inlineStr"/>
       <c r="H584" t="inlineStr"/>
       <c r="I584" t="inlineStr"/>
-      <c r="J584" t="inlineStr"/>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K584" t="inlineStr"/>
       <c r="L584" t="inlineStr">
         <is>
@@ -41876,7 +43680,11 @@
       <c r="G585" t="inlineStr"/>
       <c r="H585" t="inlineStr"/>
       <c r="I585" t="inlineStr"/>
-      <c r="J585" t="inlineStr"/>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K585" t="inlineStr"/>
       <c r="L585" t="inlineStr">
         <is>
@@ -41937,7 +43745,11 @@
       <c r="G586" t="inlineStr"/>
       <c r="H586" t="inlineStr"/>
       <c r="I586" t="inlineStr"/>
-      <c r="J586" t="inlineStr"/>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K586" t="inlineStr"/>
       <c r="L586" t="inlineStr">
         <is>
@@ -41998,7 +43810,11 @@
       <c r="G587" t="inlineStr"/>
       <c r="H587" t="inlineStr"/>
       <c r="I587" t="inlineStr"/>
-      <c r="J587" t="inlineStr"/>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr">
         <is>
@@ -42059,7 +43875,11 @@
       <c r="G588" t="inlineStr"/>
       <c r="H588" t="inlineStr"/>
       <c r="I588" t="inlineStr"/>
-      <c r="J588" t="inlineStr"/>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K588" t="inlineStr"/>
       <c r="L588" t="inlineStr">
         <is>
@@ -42120,7 +43940,11 @@
       <c r="G589" t="inlineStr"/>
       <c r="H589" t="inlineStr"/>
       <c r="I589" t="inlineStr"/>
-      <c r="J589" t="inlineStr"/>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K589" t="inlineStr"/>
       <c r="L589" t="inlineStr">
         <is>
@@ -42181,7 +44005,11 @@
       <c r="G590" t="inlineStr"/>
       <c r="H590" t="inlineStr"/>
       <c r="I590" t="inlineStr"/>
-      <c r="J590" t="inlineStr"/>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K590" t="inlineStr"/>
       <c r="L590" t="inlineStr">
         <is>
@@ -42242,7 +44070,11 @@
       <c r="G591" t="inlineStr"/>
       <c r="H591" t="inlineStr"/>
       <c r="I591" t="inlineStr"/>
-      <c r="J591" t="inlineStr"/>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K591" t="inlineStr"/>
       <c r="L591" t="inlineStr">
         <is>
@@ -42303,7 +44135,11 @@
       <c r="G592" t="inlineStr"/>
       <c r="H592" t="inlineStr"/>
       <c r="I592" t="inlineStr"/>
-      <c r="J592" t="inlineStr"/>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K592" t="inlineStr"/>
       <c r="L592" t="inlineStr">
         <is>
@@ -42364,7 +44200,11 @@
       <c r="G593" t="inlineStr"/>
       <c r="H593" t="inlineStr"/>
       <c r="I593" t="inlineStr"/>
-      <c r="J593" t="inlineStr"/>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr">
         <is>
@@ -42425,7 +44265,11 @@
       <c r="G594" t="inlineStr"/>
       <c r="H594" t="inlineStr"/>
       <c r="I594" t="inlineStr"/>
-      <c r="J594" t="inlineStr"/>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K594" t="inlineStr"/>
       <c r="L594" t="inlineStr">
         <is>
@@ -42486,7 +44330,11 @@
       <c r="G595" t="inlineStr"/>
       <c r="H595" t="inlineStr"/>
       <c r="I595" t="inlineStr"/>
-      <c r="J595" t="inlineStr"/>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K595" t="inlineStr"/>
       <c r="L595" t="inlineStr">
         <is>
@@ -42547,7 +44395,11 @@
       <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr"/>
       <c r="I596" t="inlineStr"/>
-      <c r="J596" t="inlineStr"/>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K596" t="inlineStr"/>
       <c r="L596" t="inlineStr">
         <is>
@@ -42608,7 +44460,11 @@
       <c r="G597" t="inlineStr"/>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr"/>
-      <c r="J597" t="inlineStr"/>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K597" t="inlineStr"/>
       <c r="L597" t="inlineStr">
         <is>
@@ -42669,7 +44525,11 @@
       <c r="G598" t="inlineStr"/>
       <c r="H598" t="inlineStr"/>
       <c r="I598" t="inlineStr"/>
-      <c r="J598" t="inlineStr"/>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr">
         <is>
@@ -42730,7 +44590,11 @@
       <c r="G599" t="inlineStr"/>
       <c r="H599" t="inlineStr"/>
       <c r="I599" t="inlineStr"/>
-      <c r="J599" t="inlineStr"/>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr">
         <is>
@@ -42791,7 +44655,11 @@
       <c r="G600" t="inlineStr"/>
       <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr"/>
-      <c r="J600" t="inlineStr"/>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr">
         <is>
@@ -42852,7 +44720,11 @@
       <c r="G601" t="inlineStr"/>
       <c r="H601" t="inlineStr"/>
       <c r="I601" t="inlineStr"/>
-      <c r="J601" t="inlineStr"/>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr">
         <is>
@@ -42913,7 +44785,11 @@
       <c r="G602" t="inlineStr"/>
       <c r="H602" t="inlineStr"/>
       <c r="I602" t="inlineStr"/>
-      <c r="J602" t="inlineStr"/>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr">
         <is>
@@ -42974,7 +44850,11 @@
       <c r="G603" t="inlineStr"/>
       <c r="H603" t="inlineStr"/>
       <c r="I603" t="inlineStr"/>
-      <c r="J603" t="inlineStr"/>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr">
         <is>
@@ -43035,7 +44915,11 @@
       <c r="G604" t="inlineStr"/>
       <c r="H604" t="inlineStr"/>
       <c r="I604" t="inlineStr"/>
-      <c r="J604" t="inlineStr"/>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr">
         <is>
@@ -43096,7 +44980,11 @@
       <c r="G605" t="inlineStr"/>
       <c r="H605" t="inlineStr"/>
       <c r="I605" t="inlineStr"/>
-      <c r="J605" t="inlineStr"/>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr">
         <is>
@@ -43157,7 +45045,11 @@
       <c r="G606" t="inlineStr"/>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr"/>
-      <c r="J606" t="inlineStr"/>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr">
         <is>
@@ -43218,7 +45110,11 @@
       <c r="G607" t="inlineStr"/>
       <c r="H607" t="inlineStr"/>
       <c r="I607" t="inlineStr"/>
-      <c r="J607" t="inlineStr"/>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr">
         <is>
@@ -43279,7 +45175,11 @@
       <c r="G608" t="inlineStr"/>
       <c r="H608" t="inlineStr"/>
       <c r="I608" t="inlineStr"/>
-      <c r="J608" t="inlineStr"/>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr">
         <is>
@@ -43340,7 +45240,11 @@
       <c r="G609" t="inlineStr"/>
       <c r="H609" t="inlineStr"/>
       <c r="I609" t="inlineStr"/>
-      <c r="J609" t="inlineStr"/>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr">
         <is>
@@ -43401,7 +45305,11 @@
       <c r="G610" t="inlineStr"/>
       <c r="H610" t="inlineStr"/>
       <c r="I610" t="inlineStr"/>
-      <c r="J610" t="inlineStr"/>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K610" t="inlineStr"/>
       <c r="L610" t="inlineStr">
         <is>
@@ -43462,7 +45370,11 @@
       <c r="G611" t="inlineStr"/>
       <c r="H611" t="inlineStr"/>
       <c r="I611" t="inlineStr"/>
-      <c r="J611" t="inlineStr"/>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K611" t="inlineStr"/>
       <c r="L611" t="inlineStr">
         <is>
@@ -43523,7 +45435,11 @@
       <c r="G612" t="inlineStr"/>
       <c r="H612" t="inlineStr"/>
       <c r="I612" t="inlineStr"/>
-      <c r="J612" t="inlineStr"/>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K612" t="inlineStr"/>
       <c r="L612" t="inlineStr">
         <is>
@@ -43584,7 +45500,11 @@
       <c r="G613" t="inlineStr"/>
       <c r="H613" t="inlineStr"/>
       <c r="I613" t="inlineStr"/>
-      <c r="J613" t="inlineStr"/>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K613" t="inlineStr"/>
       <c r="L613" t="inlineStr">
         <is>
@@ -43645,7 +45565,11 @@
       <c r="G614" t="inlineStr"/>
       <c r="H614" t="inlineStr"/>
       <c r="I614" t="inlineStr"/>
-      <c r="J614" t="inlineStr"/>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K614" t="inlineStr"/>
       <c r="L614" t="inlineStr">
         <is>
@@ -43706,7 +45630,11 @@
       <c r="G615" t="inlineStr"/>
       <c r="H615" t="inlineStr"/>
       <c r="I615" t="inlineStr"/>
-      <c r="J615" t="inlineStr"/>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K615" t="inlineStr"/>
       <c r="L615" t="inlineStr">
         <is>
@@ -43767,7 +45695,11 @@
       <c r="G616" t="inlineStr"/>
       <c r="H616" t="inlineStr"/>
       <c r="I616" t="inlineStr"/>
-      <c r="J616" t="inlineStr"/>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K616" t="inlineStr"/>
       <c r="L616" t="inlineStr">
         <is>
@@ -43828,7 +45760,11 @@
       <c r="G617" t="inlineStr"/>
       <c r="H617" t="inlineStr"/>
       <c r="I617" t="inlineStr"/>
-      <c r="J617" t="inlineStr"/>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K617" t="inlineStr"/>
       <c r="L617" t="inlineStr">
         <is>
@@ -43889,7 +45825,11 @@
       <c r="G618" t="inlineStr"/>
       <c r="H618" t="inlineStr"/>
       <c r="I618" t="inlineStr"/>
-      <c r="J618" t="inlineStr"/>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K618" t="inlineStr"/>
       <c r="L618" t="inlineStr">
         <is>
@@ -43950,7 +45890,11 @@
       <c r="G619" t="inlineStr"/>
       <c r="H619" t="inlineStr"/>
       <c r="I619" t="inlineStr"/>
-      <c r="J619" t="inlineStr"/>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K619" t="inlineStr"/>
       <c r="L619" t="inlineStr">
         <is>
@@ -44011,7 +45955,11 @@
       <c r="G620" t="inlineStr"/>
       <c r="H620" t="inlineStr"/>
       <c r="I620" t="inlineStr"/>
-      <c r="J620" t="inlineStr"/>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr">
         <is>
@@ -44072,7 +46020,11 @@
       <c r="G621" t="inlineStr"/>
       <c r="H621" t="inlineStr"/>
       <c r="I621" t="inlineStr"/>
-      <c r="J621" t="inlineStr"/>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K621" t="inlineStr"/>
       <c r="L621" t="inlineStr">
         <is>
@@ -44133,7 +46085,11 @@
       <c r="G622" t="inlineStr"/>
       <c r="H622" t="inlineStr"/>
       <c r="I622" t="inlineStr"/>
-      <c r="J622" t="inlineStr"/>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K622" t="inlineStr"/>
       <c r="L622" t="inlineStr">
         <is>
@@ -44194,7 +46150,11 @@
       <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr"/>
       <c r="I623" t="inlineStr"/>
-      <c r="J623" t="inlineStr"/>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K623" t="inlineStr"/>
       <c r="L623" t="inlineStr">
         <is>
@@ -44267,7 +46227,11 @@
       <c r="G624" t="inlineStr"/>
       <c r="H624" t="inlineStr"/>
       <c r="I624" t="inlineStr"/>
-      <c r="J624" t="inlineStr"/>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr">
         <is>
@@ -44344,7 +46308,11 @@
       </c>
       <c r="H625" t="inlineStr"/>
       <c r="I625" t="inlineStr"/>
-      <c r="J625" t="inlineStr"/>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr">
         <is>
@@ -44405,7 +46373,11 @@
       <c r="G626" t="inlineStr"/>
       <c r="H626" t="inlineStr"/>
       <c r="I626" t="inlineStr"/>
-      <c r="J626" t="inlineStr"/>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K626" t="inlineStr"/>
       <c r="L626" t="inlineStr">
         <is>
@@ -44466,7 +46438,11 @@
       <c r="G627" t="inlineStr"/>
       <c r="H627" t="inlineStr"/>
       <c r="I627" t="inlineStr"/>
-      <c r="J627" t="inlineStr"/>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr">
         <is>
@@ -44527,7 +46503,11 @@
       <c r="G628" t="inlineStr"/>
       <c r="H628" t="inlineStr"/>
       <c r="I628" t="inlineStr"/>
-      <c r="J628" t="inlineStr"/>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K628" t="inlineStr"/>
       <c r="L628" t="inlineStr">
         <is>
@@ -44588,7 +46568,11 @@
       <c r="G629" t="inlineStr"/>
       <c r="H629" t="inlineStr"/>
       <c r="I629" t="inlineStr"/>
-      <c r="J629" t="inlineStr"/>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K629" t="inlineStr"/>
       <c r="L629" t="inlineStr">
         <is>
@@ -44649,7 +46633,11 @@
       <c r="G630" t="inlineStr"/>
       <c r="H630" t="inlineStr"/>
       <c r="I630" t="inlineStr"/>
-      <c r="J630" t="inlineStr"/>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr">
         <is>
@@ -44710,7 +46698,11 @@
       <c r="G631" t="inlineStr"/>
       <c r="H631" t="inlineStr"/>
       <c r="I631" t="inlineStr"/>
-      <c r="J631" t="inlineStr"/>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr">
         <is>
@@ -44771,7 +46763,11 @@
       <c r="G632" t="inlineStr"/>
       <c r="H632" t="inlineStr"/>
       <c r="I632" t="inlineStr"/>
-      <c r="J632" t="inlineStr"/>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K632" t="inlineStr"/>
       <c r="L632" t="inlineStr">
         <is>
@@ -44832,7 +46828,11 @@
       <c r="G633" t="inlineStr"/>
       <c r="H633" t="inlineStr"/>
       <c r="I633" t="inlineStr"/>
-      <c r="J633" t="inlineStr"/>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K633" t="inlineStr"/>
       <c r="L633" t="inlineStr">
         <is>
@@ -44893,7 +46893,11 @@
       <c r="G634" t="inlineStr"/>
       <c r="H634" t="inlineStr"/>
       <c r="I634" t="inlineStr"/>
-      <c r="J634" t="inlineStr"/>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K634" t="inlineStr"/>
       <c r="L634" t="inlineStr">
         <is>
@@ -44954,7 +46958,11 @@
       <c r="G635" t="inlineStr"/>
       <c r="H635" t="inlineStr"/>
       <c r="I635" t="inlineStr"/>
-      <c r="J635" t="inlineStr"/>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr">
         <is>
@@ -45015,7 +47023,11 @@
       <c r="G636" t="inlineStr"/>
       <c r="H636" t="inlineStr"/>
       <c r="I636" t="inlineStr"/>
-      <c r="J636" t="inlineStr"/>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K636" t="inlineStr"/>
       <c r="L636" t="inlineStr">
         <is>
@@ -45076,7 +47088,11 @@
       <c r="G637" t="inlineStr"/>
       <c r="H637" t="inlineStr"/>
       <c r="I637" t="inlineStr"/>
-      <c r="J637" t="inlineStr"/>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K637" t="inlineStr"/>
       <c r="L637" t="inlineStr">
         <is>
@@ -45137,7 +47153,11 @@
       <c r="G638" t="inlineStr"/>
       <c r="H638" t="inlineStr"/>
       <c r="I638" t="inlineStr"/>
-      <c r="J638" t="inlineStr"/>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K638" t="inlineStr"/>
       <c r="L638" t="inlineStr">
         <is>
@@ -45198,7 +47218,11 @@
       <c r="G639" t="inlineStr"/>
       <c r="H639" t="inlineStr"/>
       <c r="I639" t="inlineStr"/>
-      <c r="J639" t="inlineStr"/>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K639" t="inlineStr"/>
       <c r="L639" t="inlineStr">
         <is>
@@ -45259,7 +47283,11 @@
       <c r="G640" t="inlineStr"/>
       <c r="H640" t="inlineStr"/>
       <c r="I640" t="inlineStr"/>
-      <c r="J640" t="inlineStr"/>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr">
         <is>
@@ -45320,7 +47348,11 @@
       <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr"/>
       <c r="I641" t="inlineStr"/>
-      <c r="J641" t="inlineStr"/>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K641" t="inlineStr"/>
       <c r="L641" t="inlineStr">
         <is>
@@ -45381,7 +47413,11 @@
       <c r="G642" t="inlineStr"/>
       <c r="H642" t="inlineStr"/>
       <c r="I642" t="inlineStr"/>
-      <c r="J642" t="inlineStr"/>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr">
         <is>
@@ -45442,7 +47478,11 @@
       <c r="G643" t="inlineStr"/>
       <c r="H643" t="inlineStr"/>
       <c r="I643" t="inlineStr"/>
-      <c r="J643" t="inlineStr"/>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr">
         <is>
@@ -45503,7 +47543,11 @@
       <c r="G644" t="inlineStr"/>
       <c r="H644" t="inlineStr"/>
       <c r="I644" t="inlineStr"/>
-      <c r="J644" t="inlineStr"/>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr">
         <is>
@@ -45564,7 +47608,11 @@
       <c r="G645" t="inlineStr"/>
       <c r="H645" t="inlineStr"/>
       <c r="I645" t="inlineStr"/>
-      <c r="J645" t="inlineStr"/>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K645" t="inlineStr"/>
       <c r="L645" t="inlineStr">
         <is>
@@ -45625,7 +47673,11 @@
       <c r="G646" t="inlineStr"/>
       <c r="H646" t="inlineStr"/>
       <c r="I646" t="inlineStr"/>
-      <c r="J646" t="inlineStr"/>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K646" t="inlineStr"/>
       <c r="L646" t="inlineStr">
         <is>
@@ -45686,7 +47738,11 @@
       <c r="G647" t="inlineStr"/>
       <c r="H647" t="inlineStr"/>
       <c r="I647" t="inlineStr"/>
-      <c r="J647" t="inlineStr"/>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr">
         <is>
@@ -45747,7 +47803,11 @@
       <c r="G648" t="inlineStr"/>
       <c r="H648" t="inlineStr"/>
       <c r="I648" t="inlineStr"/>
-      <c r="J648" t="inlineStr"/>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr">
         <is>
@@ -45808,7 +47868,11 @@
       <c r="G649" t="inlineStr"/>
       <c r="H649" t="inlineStr"/>
       <c r="I649" t="inlineStr"/>
-      <c r="J649" t="inlineStr"/>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K649" t="inlineStr"/>
       <c r="L649" t="inlineStr">
         <is>
@@ -45869,7 +47933,11 @@
       <c r="G650" t="inlineStr"/>
       <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr"/>
-      <c r="J650" t="inlineStr"/>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K650" t="inlineStr"/>
       <c r="L650" t="inlineStr">
         <is>
@@ -45930,7 +47998,11 @@
       <c r="G651" t="inlineStr"/>
       <c r="H651" t="inlineStr"/>
       <c r="I651" t="inlineStr"/>
-      <c r="J651" t="inlineStr"/>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr">
         <is>
@@ -45991,7 +48063,11 @@
       <c r="G652" t="inlineStr"/>
       <c r="H652" t="inlineStr"/>
       <c r="I652" t="inlineStr"/>
-      <c r="J652" t="inlineStr"/>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr">
         <is>
@@ -46052,7 +48128,11 @@
       <c r="G653" t="inlineStr"/>
       <c r="H653" t="inlineStr"/>
       <c r="I653" t="inlineStr"/>
-      <c r="J653" t="inlineStr"/>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr">
         <is>
@@ -46113,7 +48193,11 @@
       <c r="G654" t="inlineStr"/>
       <c r="H654" t="inlineStr"/>
       <c r="I654" t="inlineStr"/>
-      <c r="J654" t="inlineStr"/>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr">
         <is>
@@ -46174,7 +48258,11 @@
       <c r="G655" t="inlineStr"/>
       <c r="H655" t="inlineStr"/>
       <c r="I655" t="inlineStr"/>
-      <c r="J655" t="inlineStr"/>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K655" t="inlineStr"/>
       <c r="L655" t="inlineStr">
         <is>
@@ -46235,7 +48323,11 @@
       <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr"/>
       <c r="I656" t="inlineStr"/>
-      <c r="J656" t="inlineStr"/>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr">
         <is>
@@ -46296,7 +48388,11 @@
       <c r="G657" t="inlineStr"/>
       <c r="H657" t="inlineStr"/>
       <c r="I657" t="inlineStr"/>
-      <c r="J657" t="inlineStr"/>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr">
         <is>
@@ -46357,7 +48453,11 @@
       <c r="G658" t="inlineStr"/>
       <c r="H658" t="inlineStr"/>
       <c r="I658" t="inlineStr"/>
-      <c r="J658" t="inlineStr"/>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K658" t="inlineStr"/>
       <c r="L658" t="inlineStr">
         <is>
@@ -46418,7 +48518,11 @@
       <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr"/>
       <c r="I659" t="inlineStr"/>
-      <c r="J659" t="inlineStr"/>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr">
         <is>
@@ -46479,7 +48583,11 @@
       <c r="G660" t="inlineStr"/>
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr"/>
-      <c r="J660" t="inlineStr"/>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr">
         <is>
@@ -46540,7 +48648,11 @@
       <c r="G661" t="inlineStr"/>
       <c r="H661" t="inlineStr"/>
       <c r="I661" t="inlineStr"/>
-      <c r="J661" t="inlineStr"/>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr">
         <is>
@@ -46601,7 +48713,11 @@
       <c r="G662" t="inlineStr"/>
       <c r="H662" t="inlineStr"/>
       <c r="I662" t="inlineStr"/>
-      <c r="J662" t="inlineStr"/>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K662" t="inlineStr"/>
       <c r="L662" t="inlineStr">
         <is>
@@ -46662,7 +48778,11 @@
       <c r="G663" t="inlineStr"/>
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr"/>
-      <c r="J663" t="inlineStr"/>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K663" t="inlineStr"/>
       <c r="L663" t="inlineStr">
         <is>
@@ -46723,7 +48843,11 @@
       <c r="G664" t="inlineStr"/>
       <c r="H664" t="inlineStr"/>
       <c r="I664" t="inlineStr"/>
-      <c r="J664" t="inlineStr"/>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K664" t="inlineStr"/>
       <c r="L664" t="inlineStr">
         <is>
@@ -46800,7 +48924,11 @@
       </c>
       <c r="H665" t="inlineStr"/>
       <c r="I665" t="inlineStr"/>
-      <c r="J665" t="inlineStr"/>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K665" t="inlineStr"/>
       <c r="L665" t="inlineStr">
         <is>
@@ -46861,7 +48989,11 @@
       <c r="G666" t="inlineStr"/>
       <c r="H666" t="inlineStr"/>
       <c r="I666" t="inlineStr"/>
-      <c r="J666" t="inlineStr"/>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr">
         <is>
@@ -46922,7 +49054,11 @@
       <c r="G667" t="inlineStr"/>
       <c r="H667" t="inlineStr"/>
       <c r="I667" t="inlineStr"/>
-      <c r="J667" t="inlineStr"/>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K667" t="inlineStr"/>
       <c r="L667" t="inlineStr">
         <is>
@@ -46983,7 +49119,11 @@
       <c r="G668" t="inlineStr"/>
       <c r="H668" t="inlineStr"/>
       <c r="I668" t="inlineStr"/>
-      <c r="J668" t="inlineStr"/>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K668" t="inlineStr"/>
       <c r="L668" t="inlineStr">
         <is>
@@ -47044,7 +49184,11 @@
       <c r="G669" t="inlineStr"/>
       <c r="H669" t="inlineStr"/>
       <c r="I669" t="inlineStr"/>
-      <c r="J669" t="inlineStr"/>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K669" t="inlineStr"/>
       <c r="L669" t="inlineStr">
         <is>
@@ -47105,7 +49249,11 @@
       <c r="G670" t="inlineStr"/>
       <c r="H670" t="inlineStr"/>
       <c r="I670" t="inlineStr"/>
-      <c r="J670" t="inlineStr"/>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K670" t="inlineStr"/>
       <c r="L670" t="inlineStr">
         <is>
@@ -47166,7 +49314,11 @@
       <c r="G671" t="inlineStr"/>
       <c r="H671" t="inlineStr"/>
       <c r="I671" t="inlineStr"/>
-      <c r="J671" t="inlineStr"/>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr">
         <is>
@@ -47227,7 +49379,11 @@
       <c r="G672" t="inlineStr"/>
       <c r="H672" t="inlineStr"/>
       <c r="I672" t="inlineStr"/>
-      <c r="J672" t="inlineStr"/>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K672" t="inlineStr"/>
       <c r="L672" t="inlineStr">
         <is>
@@ -47288,7 +49444,11 @@
       <c r="G673" t="inlineStr"/>
       <c r="H673" t="inlineStr"/>
       <c r="I673" t="inlineStr"/>
-      <c r="J673" t="inlineStr"/>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K673" t="inlineStr"/>
       <c r="L673" t="inlineStr">
         <is>
@@ -47349,7 +49509,11 @@
       <c r="G674" t="inlineStr"/>
       <c r="H674" t="inlineStr"/>
       <c r="I674" t="inlineStr"/>
-      <c r="J674" t="inlineStr"/>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K674" t="inlineStr"/>
       <c r="L674" t="inlineStr">
         <is>
@@ -47410,7 +49574,11 @@
       <c r="G675" t="inlineStr"/>
       <c r="H675" t="inlineStr"/>
       <c r="I675" t="inlineStr"/>
-      <c r="J675" t="inlineStr"/>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K675" t="inlineStr"/>
       <c r="L675" t="inlineStr">
         <is>
@@ -47471,7 +49639,11 @@
       <c r="G676" t="inlineStr"/>
       <c r="H676" t="inlineStr"/>
       <c r="I676" t="inlineStr"/>
-      <c r="J676" t="inlineStr"/>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K676" t="inlineStr"/>
       <c r="L676" t="inlineStr">
         <is>
@@ -47532,7 +49704,11 @@
       <c r="G677" t="inlineStr"/>
       <c r="H677" t="inlineStr"/>
       <c r="I677" t="inlineStr"/>
-      <c r="J677" t="inlineStr"/>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K677" t="inlineStr"/>
       <c r="L677" t="inlineStr">
         <is>
@@ -47593,7 +49769,11 @@
       <c r="G678" t="inlineStr"/>
       <c r="H678" t="inlineStr"/>
       <c r="I678" t="inlineStr"/>
-      <c r="J678" t="inlineStr"/>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K678" t="inlineStr"/>
       <c r="L678" t="inlineStr">
         <is>
@@ -47654,7 +49834,11 @@
       <c r="G679" t="inlineStr"/>
       <c r="H679" t="inlineStr"/>
       <c r="I679" t="inlineStr"/>
-      <c r="J679" t="inlineStr"/>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K679" t="inlineStr"/>
       <c r="L679" t="inlineStr">
         <is>
@@ -47715,7 +49899,11 @@
       <c r="G680" t="inlineStr"/>
       <c r="H680" t="inlineStr"/>
       <c r="I680" t="inlineStr"/>
-      <c r="J680" t="inlineStr"/>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr">
         <is>
@@ -47776,7 +49964,11 @@
       <c r="G681" t="inlineStr"/>
       <c r="H681" t="inlineStr"/>
       <c r="I681" t="inlineStr"/>
-      <c r="J681" t="inlineStr"/>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K681" t="inlineStr"/>
       <c r="L681" t="inlineStr">
         <is>
@@ -47837,7 +50029,11 @@
       <c r="G682" t="inlineStr"/>
       <c r="H682" t="inlineStr"/>
       <c r="I682" t="inlineStr"/>
-      <c r="J682" t="inlineStr"/>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr">
         <is>
@@ -47898,7 +50094,11 @@
       <c r="G683" t="inlineStr"/>
       <c r="H683" t="inlineStr"/>
       <c r="I683" t="inlineStr"/>
-      <c r="J683" t="inlineStr"/>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr">
         <is>
@@ -47971,7 +50171,11 @@
       </c>
       <c r="H684" t="inlineStr"/>
       <c r="I684" t="inlineStr"/>
-      <c r="J684" t="inlineStr"/>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K684" t="inlineStr"/>
       <c r="L684" t="inlineStr">
         <is>
@@ -48032,7 +50236,11 @@
       <c r="G685" t="inlineStr"/>
       <c r="H685" t="inlineStr"/>
       <c r="I685" t="inlineStr"/>
-      <c r="J685" t="inlineStr"/>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K685" t="inlineStr"/>
       <c r="L685" t="inlineStr">
         <is>
@@ -48093,7 +50301,11 @@
       <c r="G686" t="inlineStr"/>
       <c r="H686" t="inlineStr"/>
       <c r="I686" t="inlineStr"/>
-      <c r="J686" t="inlineStr"/>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr">
         <is>
@@ -48154,7 +50366,11 @@
       <c r="G687" t="inlineStr"/>
       <c r="H687" t="inlineStr"/>
       <c r="I687" t="inlineStr"/>
-      <c r="J687" t="inlineStr"/>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K687" t="inlineStr"/>
       <c r="L687" t="inlineStr">
         <is>
@@ -48215,7 +50431,11 @@
       <c r="G688" t="inlineStr"/>
       <c r="H688" t="inlineStr"/>
       <c r="I688" t="inlineStr"/>
-      <c r="J688" t="inlineStr"/>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K688" t="inlineStr"/>
       <c r="L688" t="inlineStr">
         <is>
@@ -48276,7 +50496,11 @@
       <c r="G689" t="inlineStr"/>
       <c r="H689" t="inlineStr"/>
       <c r="I689" t="inlineStr"/>
-      <c r="J689" t="inlineStr"/>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr">
         <is>
@@ -48337,7 +50561,11 @@
       <c r="G690" t="inlineStr"/>
       <c r="H690" t="inlineStr"/>
       <c r="I690" t="inlineStr"/>
-      <c r="J690" t="inlineStr"/>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr">
         <is>
@@ -48398,7 +50626,11 @@
       <c r="G691" t="inlineStr"/>
       <c r="H691" t="inlineStr"/>
       <c r="I691" t="inlineStr"/>
-      <c r="J691" t="inlineStr"/>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr">
         <is>
@@ -48459,7 +50691,11 @@
       <c r="G692" t="inlineStr"/>
       <c r="H692" t="inlineStr"/>
       <c r="I692" t="inlineStr"/>
-      <c r="J692" t="inlineStr"/>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K692" t="inlineStr"/>
       <c r="L692" t="inlineStr">
         <is>
@@ -48520,7 +50756,11 @@
       <c r="G693" t="inlineStr"/>
       <c r="H693" t="inlineStr"/>
       <c r="I693" t="inlineStr"/>
-      <c r="J693" t="inlineStr"/>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K693" t="inlineStr"/>
       <c r="L693" t="inlineStr">
         <is>
@@ -48581,7 +50821,11 @@
       <c r="G694" t="inlineStr"/>
       <c r="H694" t="inlineStr"/>
       <c r="I694" t="inlineStr"/>
-      <c r="J694" t="inlineStr"/>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K694" t="inlineStr"/>
       <c r="L694" t="inlineStr">
         <is>
@@ -48642,7 +50886,11 @@
       <c r="G695" t="inlineStr"/>
       <c r="H695" t="inlineStr"/>
       <c r="I695" t="inlineStr"/>
-      <c r="J695" t="inlineStr"/>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K695" t="inlineStr"/>
       <c r="L695" t="inlineStr">
         <is>
@@ -48703,7 +50951,11 @@
       <c r="G696" t="inlineStr"/>
       <c r="H696" t="inlineStr"/>
       <c r="I696" t="inlineStr"/>
-      <c r="J696" t="inlineStr"/>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K696" t="inlineStr"/>
       <c r="L696" t="inlineStr">
         <is>
@@ -48764,7 +51016,11 @@
       <c r="G697" t="inlineStr"/>
       <c r="H697" t="inlineStr"/>
       <c r="I697" t="inlineStr"/>
-      <c r="J697" t="inlineStr"/>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K697" t="inlineStr"/>
       <c r="L697" t="inlineStr">
         <is>
@@ -48825,7 +51081,11 @@
       <c r="G698" t="inlineStr"/>
       <c r="H698" t="inlineStr"/>
       <c r="I698" t="inlineStr"/>
-      <c r="J698" t="inlineStr"/>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K698" t="inlineStr"/>
       <c r="L698" t="inlineStr">
         <is>
@@ -48886,7 +51146,11 @@
       <c r="G699" t="inlineStr"/>
       <c r="H699" t="inlineStr"/>
       <c r="I699" t="inlineStr"/>
-      <c r="J699" t="inlineStr"/>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr">
         <is>
@@ -48947,7 +51211,11 @@
       <c r="G700" t="inlineStr"/>
       <c r="H700" t="inlineStr"/>
       <c r="I700" t="inlineStr"/>
-      <c r="J700" t="inlineStr"/>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K700" t="inlineStr"/>
       <c r="L700" t="inlineStr">
         <is>
@@ -49008,7 +51276,11 @@
       <c r="G701" t="inlineStr"/>
       <c r="H701" t="inlineStr"/>
       <c r="I701" t="inlineStr"/>
-      <c r="J701" t="inlineStr"/>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="inlineStr">
         <is>
@@ -49069,7 +51341,11 @@
       <c r="G702" t="inlineStr"/>
       <c r="H702" t="inlineStr"/>
       <c r="I702" t="inlineStr"/>
-      <c r="J702" t="inlineStr"/>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr">
         <is>
@@ -49130,7 +51406,11 @@
       <c r="G703" t="inlineStr"/>
       <c r="H703" t="inlineStr"/>
       <c r="I703" t="inlineStr"/>
-      <c r="J703" t="inlineStr"/>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr">
         <is>
@@ -49191,7 +51471,11 @@
       <c r="G704" t="inlineStr"/>
       <c r="H704" t="inlineStr"/>
       <c r="I704" t="inlineStr"/>
-      <c r="J704" t="inlineStr"/>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K704" t="inlineStr"/>
       <c r="L704" t="inlineStr">
         <is>
@@ -49252,7 +51536,11 @@
       <c r="G705" t="inlineStr"/>
       <c r="H705" t="inlineStr"/>
       <c r="I705" t="inlineStr"/>
-      <c r="J705" t="inlineStr"/>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K705" t="inlineStr"/>
       <c r="L705" t="inlineStr">
         <is>
@@ -49313,7 +51601,11 @@
       <c r="G706" t="inlineStr"/>
       <c r="H706" t="inlineStr"/>
       <c r="I706" t="inlineStr"/>
-      <c r="J706" t="inlineStr"/>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K706" t="inlineStr"/>
       <c r="L706" t="inlineStr">
         <is>
@@ -49374,7 +51666,11 @@
       <c r="G707" t="inlineStr"/>
       <c r="H707" t="inlineStr"/>
       <c r="I707" t="inlineStr"/>
-      <c r="J707" t="inlineStr"/>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K707" t="inlineStr"/>
       <c r="L707" t="inlineStr">
         <is>
@@ -49435,7 +51731,11 @@
       <c r="G708" t="inlineStr"/>
       <c r="H708" t="inlineStr"/>
       <c r="I708" t="inlineStr"/>
-      <c r="J708" t="inlineStr"/>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr">
         <is>
@@ -49496,7 +51796,11 @@
       <c r="G709" t="inlineStr"/>
       <c r="H709" t="inlineStr"/>
       <c r="I709" t="inlineStr"/>
-      <c r="J709" t="inlineStr"/>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K709" t="inlineStr"/>
       <c r="L709" t="inlineStr">
         <is>
@@ -49557,7 +51861,11 @@
       <c r="G710" t="inlineStr"/>
       <c r="H710" t="inlineStr"/>
       <c r="I710" t="inlineStr"/>
-      <c r="J710" t="inlineStr"/>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K710" t="inlineStr"/>
       <c r="L710" t="inlineStr">
         <is>
@@ -49618,7 +51926,11 @@
       <c r="G711" t="inlineStr"/>
       <c r="H711" t="inlineStr"/>
       <c r="I711" t="inlineStr"/>
-      <c r="J711" t="inlineStr"/>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr">
         <is>
@@ -49679,7 +51991,11 @@
       <c r="G712" t="inlineStr"/>
       <c r="H712" t="inlineStr"/>
       <c r="I712" t="inlineStr"/>
-      <c r="J712" t="inlineStr"/>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K712" t="inlineStr"/>
       <c r="L712" t="inlineStr">
         <is>
@@ -49740,7 +52056,11 @@
       <c r="G713" t="inlineStr"/>
       <c r="H713" t="inlineStr"/>
       <c r="I713" t="inlineStr"/>
-      <c r="J713" t="inlineStr"/>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K713" t="inlineStr"/>
       <c r="L713" t="inlineStr">
         <is>
@@ -49801,7 +52121,11 @@
       <c r="G714" t="inlineStr"/>
       <c r="H714" t="inlineStr"/>
       <c r="I714" t="inlineStr"/>
-      <c r="J714" t="inlineStr"/>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K714" t="inlineStr"/>
       <c r="L714" t="inlineStr">
         <is>
@@ -49862,7 +52186,11 @@
       <c r="G715" t="inlineStr"/>
       <c r="H715" t="inlineStr"/>
       <c r="I715" t="inlineStr"/>
-      <c r="J715" t="inlineStr"/>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K715" t="inlineStr"/>
       <c r="L715" t="inlineStr">
         <is>
@@ -49923,7 +52251,11 @@
       <c r="G716" t="inlineStr"/>
       <c r="H716" t="inlineStr"/>
       <c r="I716" t="inlineStr"/>
-      <c r="J716" t="inlineStr"/>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K716" t="inlineStr"/>
       <c r="L716" t="inlineStr">
         <is>
@@ -49984,7 +52316,11 @@
       <c r="G717" t="inlineStr"/>
       <c r="H717" t="inlineStr"/>
       <c r="I717" t="inlineStr"/>
-      <c r="J717" t="inlineStr"/>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K717" t="inlineStr"/>
       <c r="L717" t="inlineStr">
         <is>
@@ -50045,7 +52381,11 @@
       <c r="G718" t="inlineStr"/>
       <c r="H718" t="inlineStr"/>
       <c r="I718" t="inlineStr"/>
-      <c r="J718" t="inlineStr"/>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K718" t="inlineStr"/>
       <c r="L718" t="inlineStr">
         <is>
@@ -50106,7 +52446,11 @@
       <c r="G719" t="inlineStr"/>
       <c r="H719" t="inlineStr"/>
       <c r="I719" t="inlineStr"/>
-      <c r="J719" t="inlineStr"/>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K719" t="inlineStr"/>
       <c r="L719" t="inlineStr">
         <is>
@@ -50167,7 +52511,11 @@
       <c r="G720" t="inlineStr"/>
       <c r="H720" t="inlineStr"/>
       <c r="I720" t="inlineStr"/>
-      <c r="J720" t="inlineStr"/>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K720" t="inlineStr"/>
       <c r="L720" t="inlineStr">
         <is>
@@ -50228,7 +52576,11 @@
       <c r="G721" t="inlineStr"/>
       <c r="H721" t="inlineStr"/>
       <c r="I721" t="inlineStr"/>
-      <c r="J721" t="inlineStr"/>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K721" t="inlineStr"/>
       <c r="L721" t="inlineStr">
         <is>
@@ -50289,7 +52641,11 @@
       <c r="G722" t="inlineStr"/>
       <c r="H722" t="inlineStr"/>
       <c r="I722" t="inlineStr"/>
-      <c r="J722" t="inlineStr"/>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K722" t="inlineStr"/>
       <c r="L722" t="inlineStr">
         <is>
@@ -50350,7 +52706,11 @@
       <c r="G723" t="inlineStr"/>
       <c r="H723" t="inlineStr"/>
       <c r="I723" t="inlineStr"/>
-      <c r="J723" t="inlineStr"/>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr">
         <is>
@@ -50411,7 +52771,11 @@
       <c r="G724" t="inlineStr"/>
       <c r="H724" t="inlineStr"/>
       <c r="I724" t="inlineStr"/>
-      <c r="J724" t="inlineStr"/>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K724" t="inlineStr"/>
       <c r="L724" t="inlineStr">
         <is>
@@ -50472,7 +52836,11 @@
       <c r="G725" t="inlineStr"/>
       <c r="H725" t="inlineStr"/>
       <c r="I725" t="inlineStr"/>
-      <c r="J725" t="inlineStr"/>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K725" t="inlineStr"/>
       <c r="L725" t="inlineStr">
         <is>
@@ -50533,7 +52901,11 @@
       <c r="G726" t="inlineStr"/>
       <c r="H726" t="inlineStr"/>
       <c r="I726" t="inlineStr"/>
-      <c r="J726" t="inlineStr"/>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K726" t="inlineStr"/>
       <c r="L726" t="inlineStr">
         <is>
@@ -50594,7 +52966,11 @@
       <c r="G727" t="inlineStr"/>
       <c r="H727" t="inlineStr"/>
       <c r="I727" t="inlineStr"/>
-      <c r="J727" t="inlineStr"/>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K727" t="inlineStr"/>
       <c r="L727" t="inlineStr">
         <is>
@@ -50655,7 +53031,11 @@
       <c r="G728" t="inlineStr"/>
       <c r="H728" t="inlineStr"/>
       <c r="I728" t="inlineStr"/>
-      <c r="J728" t="inlineStr"/>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K728" t="inlineStr"/>
       <c r="L728" t="inlineStr">
         <is>
@@ -50716,7 +53096,11 @@
       <c r="G729" t="inlineStr"/>
       <c r="H729" t="inlineStr"/>
       <c r="I729" t="inlineStr"/>
-      <c r="J729" t="inlineStr"/>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K729" t="inlineStr"/>
       <c r="L729" t="inlineStr">
         <is>
@@ -50777,7 +53161,11 @@
       <c r="G730" t="inlineStr"/>
       <c r="H730" t="inlineStr"/>
       <c r="I730" t="inlineStr"/>
-      <c r="J730" t="inlineStr"/>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K730" t="inlineStr"/>
       <c r="L730" t="inlineStr">
         <is>
@@ -50838,7 +53226,11 @@
       <c r="G731" t="inlineStr"/>
       <c r="H731" t="inlineStr"/>
       <c r="I731" t="inlineStr"/>
-      <c r="J731" t="inlineStr"/>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr">
         <is>
@@ -50899,7 +53291,11 @@
       <c r="G732" t="inlineStr"/>
       <c r="H732" t="inlineStr"/>
       <c r="I732" t="inlineStr"/>
-      <c r="J732" t="inlineStr"/>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K732" t="inlineStr"/>
       <c r="L732" t="inlineStr">
         <is>
@@ -50960,7 +53356,11 @@
       <c r="G733" t="inlineStr"/>
       <c r="H733" t="inlineStr"/>
       <c r="I733" t="inlineStr"/>
-      <c r="J733" t="inlineStr"/>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K733" t="inlineStr"/>
       <c r="L733" t="inlineStr">
         <is>
@@ -51021,7 +53421,11 @@
       <c r="G734" t="inlineStr"/>
       <c r="H734" t="inlineStr"/>
       <c r="I734" t="inlineStr"/>
-      <c r="J734" t="inlineStr"/>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K734" t="inlineStr"/>
       <c r="L734" t="inlineStr">
         <is>
@@ -51082,7 +53486,11 @@
       <c r="G735" t="inlineStr"/>
       <c r="H735" t="inlineStr"/>
       <c r="I735" t="inlineStr"/>
-      <c r="J735" t="inlineStr"/>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K735" t="inlineStr"/>
       <c r="L735" t="inlineStr">
         <is>
@@ -51143,7 +53551,11 @@
       <c r="G736" t="inlineStr"/>
       <c r="H736" t="inlineStr"/>
       <c r="I736" t="inlineStr"/>
-      <c r="J736" t="inlineStr"/>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K736" t="inlineStr"/>
       <c r="L736" t="inlineStr">
         <is>
@@ -51204,7 +53616,11 @@
       <c r="G737" t="inlineStr"/>
       <c r="H737" t="inlineStr"/>
       <c r="I737" t="inlineStr"/>
-      <c r="J737" t="inlineStr"/>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K737" t="inlineStr"/>
       <c r="L737" t="inlineStr">
         <is>
@@ -51265,7 +53681,11 @@
       <c r="G738" t="inlineStr"/>
       <c r="H738" t="inlineStr"/>
       <c r="I738" t="inlineStr"/>
-      <c r="J738" t="inlineStr"/>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K738" t="inlineStr"/>
       <c r="L738" t="inlineStr">
         <is>
@@ -51326,7 +53746,11 @@
       <c r="G739" t="inlineStr"/>
       <c r="H739" t="inlineStr"/>
       <c r="I739" t="inlineStr"/>
-      <c r="J739" t="inlineStr"/>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K739" t="inlineStr"/>
       <c r="L739" t="inlineStr">
         <is>
@@ -51387,7 +53811,11 @@
       <c r="G740" t="inlineStr"/>
       <c r="H740" t="inlineStr"/>
       <c r="I740" t="inlineStr"/>
-      <c r="J740" t="inlineStr"/>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K740" t="inlineStr"/>
       <c r="L740" t="inlineStr">
         <is>
@@ -51448,7 +53876,11 @@
       <c r="G741" t="inlineStr"/>
       <c r="H741" t="inlineStr"/>
       <c r="I741" t="inlineStr"/>
-      <c r="J741" t="inlineStr"/>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr">
         <is>
@@ -51509,7 +53941,11 @@
       <c r="G742" t="inlineStr"/>
       <c r="H742" t="inlineStr"/>
       <c r="I742" t="inlineStr"/>
-      <c r="J742" t="inlineStr"/>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K742" t="inlineStr"/>
       <c r="L742" t="inlineStr">
         <is>
@@ -51570,7 +54006,11 @@
       <c r="G743" t="inlineStr"/>
       <c r="H743" t="inlineStr"/>
       <c r="I743" t="inlineStr"/>
-      <c r="J743" t="inlineStr"/>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K743" t="inlineStr"/>
       <c r="L743" t="inlineStr">
         <is>
@@ -51631,7 +54071,11 @@
       <c r="G744" t="inlineStr"/>
       <c r="H744" t="inlineStr"/>
       <c r="I744" t="inlineStr"/>
-      <c r="J744" t="inlineStr"/>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K744" t="inlineStr"/>
       <c r="L744" t="inlineStr">
         <is>
@@ -51692,7 +54136,11 @@
       <c r="G745" t="inlineStr"/>
       <c r="H745" t="inlineStr"/>
       <c r="I745" t="inlineStr"/>
-      <c r="J745" t="inlineStr"/>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K745" t="inlineStr"/>
       <c r="L745" t="inlineStr">
         <is>
@@ -51753,7 +54201,11 @@
       <c r="G746" t="inlineStr"/>
       <c r="H746" t="inlineStr"/>
       <c r="I746" t="inlineStr"/>
-      <c r="J746" t="inlineStr"/>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K746" t="inlineStr"/>
       <c r="L746" t="inlineStr">
         <is>
@@ -51814,7 +54266,11 @@
       <c r="G747" t="inlineStr"/>
       <c r="H747" t="inlineStr"/>
       <c r="I747" t="inlineStr"/>
-      <c r="J747" t="inlineStr"/>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K747" t="inlineStr"/>
       <c r="L747" t="inlineStr">
         <is>
@@ -51875,7 +54331,11 @@
       <c r="G748" t="inlineStr"/>
       <c r="H748" t="inlineStr"/>
       <c r="I748" t="inlineStr"/>
-      <c r="J748" t="inlineStr"/>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K748" t="inlineStr"/>
       <c r="L748" t="inlineStr">
         <is>
@@ -51936,7 +54396,11 @@
       <c r="G749" t="inlineStr"/>
       <c r="H749" t="inlineStr"/>
       <c r="I749" t="inlineStr"/>
-      <c r="J749" t="inlineStr"/>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K749" t="inlineStr"/>
       <c r="L749" t="inlineStr">
         <is>
@@ -51997,7 +54461,11 @@
       <c r="G750" t="inlineStr"/>
       <c r="H750" t="inlineStr"/>
       <c r="I750" t="inlineStr"/>
-      <c r="J750" t="inlineStr"/>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K750" t="inlineStr"/>
       <c r="L750" t="inlineStr">
         <is>
@@ -52058,7 +54526,11 @@
       <c r="G751" t="inlineStr"/>
       <c r="H751" t="inlineStr"/>
       <c r="I751" t="inlineStr"/>
-      <c r="J751" t="inlineStr"/>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K751" t="inlineStr"/>
       <c r="L751" t="inlineStr">
         <is>
@@ -52119,7 +54591,11 @@
       <c r="G752" t="inlineStr"/>
       <c r="H752" t="inlineStr"/>
       <c r="I752" t="inlineStr"/>
-      <c r="J752" t="inlineStr"/>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K752" t="inlineStr"/>
       <c r="L752" t="inlineStr">
         <is>
@@ -52180,7 +54656,11 @@
       <c r="G753" t="inlineStr"/>
       <c r="H753" t="inlineStr"/>
       <c r="I753" t="inlineStr"/>
-      <c r="J753" t="inlineStr"/>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K753" t="inlineStr"/>
       <c r="L753" t="inlineStr">
         <is>
@@ -52241,7 +54721,11 @@
       <c r="G754" t="inlineStr"/>
       <c r="H754" t="inlineStr"/>
       <c r="I754" t="inlineStr"/>
-      <c r="J754" t="inlineStr"/>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K754" t="inlineStr"/>
       <c r="L754" t="inlineStr">
         <is>
@@ -52302,7 +54786,11 @@
       <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr"/>
       <c r="I755" t="inlineStr"/>
-      <c r="J755" t="inlineStr"/>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr">
         <is>
@@ -52363,7 +54851,11 @@
       <c r="G756" t="inlineStr"/>
       <c r="H756" t="inlineStr"/>
       <c r="I756" t="inlineStr"/>
-      <c r="J756" t="inlineStr"/>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K756" t="inlineStr"/>
       <c r="L756" t="inlineStr">
         <is>
@@ -52424,7 +54916,11 @@
       <c r="G757" t="inlineStr"/>
       <c r="H757" t="inlineStr"/>
       <c r="I757" t="inlineStr"/>
-      <c r="J757" t="inlineStr"/>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr">
         <is>
@@ -52485,7 +54981,11 @@
       <c r="G758" t="inlineStr"/>
       <c r="H758" t="inlineStr"/>
       <c r="I758" t="inlineStr"/>
-      <c r="J758" t="inlineStr"/>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr">
         <is>
@@ -52546,7 +55046,11 @@
       <c r="G759" t="inlineStr"/>
       <c r="H759" t="inlineStr"/>
       <c r="I759" t="inlineStr"/>
-      <c r="J759" t="inlineStr"/>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr">
         <is>
@@ -52607,7 +55111,11 @@
       <c r="G760" t="inlineStr"/>
       <c r="H760" t="inlineStr"/>
       <c r="I760" t="inlineStr"/>
-      <c r="J760" t="inlineStr"/>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K760" t="inlineStr"/>
       <c r="L760" t="inlineStr">
         <is>
@@ -52668,7 +55176,11 @@
       <c r="G761" t="inlineStr"/>
       <c r="H761" t="inlineStr"/>
       <c r="I761" t="inlineStr"/>
-      <c r="J761" t="inlineStr"/>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="inlineStr">
         <is>
@@ -52729,7 +55241,11 @@
       <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr"/>
       <c r="I762" t="inlineStr"/>
-      <c r="J762" t="inlineStr"/>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K762" t="inlineStr"/>
       <c r="L762" t="inlineStr">
         <is>
@@ -52790,7 +55306,11 @@
       <c r="G763" t="inlineStr"/>
       <c r="H763" t="inlineStr"/>
       <c r="I763" t="inlineStr"/>
-      <c r="J763" t="inlineStr"/>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K763" t="inlineStr"/>
       <c r="L763" t="inlineStr">
         <is>
@@ -52851,7 +55371,11 @@
       <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr"/>
       <c r="I764" t="inlineStr"/>
-      <c r="J764" t="inlineStr"/>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K764" t="inlineStr"/>
       <c r="L764" t="inlineStr">
         <is>
@@ -53013,7 +55537,11 @@
       <c r="G766" t="inlineStr"/>
       <c r="H766" t="inlineStr"/>
       <c r="I766" t="inlineStr"/>
-      <c r="J766" t="inlineStr"/>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K766" t="inlineStr"/>
       <c r="L766" t="inlineStr">
         <is>
@@ -53074,7 +55602,11 @@
       <c r="G767" t="inlineStr"/>
       <c r="H767" t="inlineStr"/>
       <c r="I767" t="inlineStr"/>
-      <c r="J767" t="inlineStr"/>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K767" t="inlineStr"/>
       <c r="L767" t="inlineStr">
         <is>
@@ -53135,7 +55667,11 @@
       <c r="G768" t="inlineStr"/>
       <c r="H768" t="inlineStr"/>
       <c r="I768" t="inlineStr"/>
-      <c r="J768" t="inlineStr"/>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr">
         <is>
@@ -53196,7 +55732,11 @@
       <c r="G769" t="inlineStr"/>
       <c r="H769" t="inlineStr"/>
       <c r="I769" t="inlineStr"/>
-      <c r="J769" t="inlineStr"/>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K769" t="inlineStr"/>
       <c r="L769" t="inlineStr">
         <is>
@@ -53257,7 +55797,11 @@
       <c r="G770" t="inlineStr"/>
       <c r="H770" t="inlineStr"/>
       <c r="I770" t="inlineStr"/>
-      <c r="J770" t="inlineStr"/>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K770" t="inlineStr"/>
       <c r="L770" t="inlineStr">
         <is>
@@ -53318,7 +55862,11 @@
       <c r="G771" t="inlineStr"/>
       <c r="H771" t="inlineStr"/>
       <c r="I771" t="inlineStr"/>
-      <c r="J771" t="inlineStr"/>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K771" t="inlineStr"/>
       <c r="L771" t="inlineStr">
         <is>
@@ -53387,7 +55935,11 @@
       <c r="G772" t="inlineStr"/>
       <c r="H772" t="inlineStr"/>
       <c r="I772" t="inlineStr"/>
-      <c r="J772" t="inlineStr"/>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K772" t="inlineStr"/>
       <c r="L772" t="inlineStr">
         <is>
@@ -53448,7 +56000,11 @@
       <c r="G773" t="inlineStr"/>
       <c r="H773" t="inlineStr"/>
       <c r="I773" t="inlineStr"/>
-      <c r="J773" t="inlineStr"/>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K773" t="inlineStr"/>
       <c r="L773" t="inlineStr">
         <is>
@@ -53525,7 +56081,11 @@
       </c>
       <c r="H774" t="inlineStr"/>
       <c r="I774" t="inlineStr"/>
-      <c r="J774" t="inlineStr"/>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K774" t="inlineStr"/>
       <c r="L774" t="inlineStr">
         <is>
@@ -53586,7 +56146,11 @@
       <c r="G775" t="inlineStr"/>
       <c r="H775" t="inlineStr"/>
       <c r="I775" t="inlineStr"/>
-      <c r="J775" t="inlineStr"/>
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K775" t="inlineStr"/>
       <c r="L775" t="inlineStr">
         <is>
@@ -53647,7 +56211,11 @@
       <c r="G776" t="inlineStr"/>
       <c r="H776" t="inlineStr"/>
       <c r="I776" t="inlineStr"/>
-      <c r="J776" t="inlineStr"/>
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K776" t="inlineStr"/>
       <c r="L776" t="inlineStr">
         <is>
@@ -53708,7 +56276,11 @@
       <c r="G777" t="inlineStr"/>
       <c r="H777" t="inlineStr"/>
       <c r="I777" t="inlineStr"/>
-      <c r="J777" t="inlineStr"/>
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K777" t="inlineStr"/>
       <c r="L777" t="inlineStr">
         <is>
@@ -53769,7 +56341,11 @@
       <c r="G778" t="inlineStr"/>
       <c r="H778" t="inlineStr"/>
       <c r="I778" t="inlineStr"/>
-      <c r="J778" t="inlineStr"/>
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K778" t="inlineStr"/>
       <c r="L778" t="inlineStr">
         <is>
@@ -53830,7 +56406,11 @@
       <c r="G779" t="inlineStr"/>
       <c r="H779" t="inlineStr"/>
       <c r="I779" t="inlineStr"/>
-      <c r="J779" t="inlineStr"/>
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K779" t="inlineStr"/>
       <c r="L779" t="inlineStr">
         <is>
@@ -53891,7 +56471,11 @@
       <c r="G780" t="inlineStr"/>
       <c r="H780" t="inlineStr"/>
       <c r="I780" t="inlineStr"/>
-      <c r="J780" t="inlineStr"/>
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K780" t="inlineStr"/>
       <c r="L780" t="inlineStr">
         <is>
@@ -53952,7 +56536,11 @@
       <c r="G781" t="inlineStr"/>
       <c r="H781" t="inlineStr"/>
       <c r="I781" t="inlineStr"/>
-      <c r="J781" t="inlineStr"/>
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K781" t="inlineStr"/>
       <c r="L781" t="inlineStr">
         <is>
@@ -54013,7 +56601,11 @@
       <c r="G782" t="inlineStr"/>
       <c r="H782" t="inlineStr"/>
       <c r="I782" t="inlineStr"/>
-      <c r="J782" t="inlineStr"/>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K782" t="inlineStr"/>
       <c r="L782" t="inlineStr">
         <is>
@@ -54074,7 +56666,11 @@
       <c r="G783" t="inlineStr"/>
       <c r="H783" t="inlineStr"/>
       <c r="I783" t="inlineStr"/>
-      <c r="J783" t="inlineStr"/>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K783" t="inlineStr"/>
       <c r="L783" t="inlineStr">
         <is>
@@ -54135,7 +56731,11 @@
       <c r="G784" t="inlineStr"/>
       <c r="H784" t="inlineStr"/>
       <c r="I784" t="inlineStr"/>
-      <c r="J784" t="inlineStr"/>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K784" t="inlineStr"/>
       <c r="L784" t="inlineStr">
         <is>
@@ -54196,7 +56796,11 @@
       <c r="G785" t="inlineStr"/>
       <c r="H785" t="inlineStr"/>
       <c r="I785" t="inlineStr"/>
-      <c r="J785" t="inlineStr"/>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K785" t="inlineStr"/>
       <c r="L785" t="inlineStr">
         <is>
@@ -54257,7 +56861,11 @@
       <c r="G786" t="inlineStr"/>
       <c r="H786" t="inlineStr"/>
       <c r="I786" t="inlineStr"/>
-      <c r="J786" t="inlineStr"/>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr">
         <is>
@@ -54318,7 +56926,11 @@
       <c r="G787" t="inlineStr"/>
       <c r="H787" t="inlineStr"/>
       <c r="I787" t="inlineStr"/>
-      <c r="J787" t="inlineStr"/>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K787" t="inlineStr"/>
       <c r="L787" t="inlineStr">
         <is>
@@ -54379,7 +56991,11 @@
       <c r="G788" t="inlineStr"/>
       <c r="H788" t="inlineStr"/>
       <c r="I788" t="inlineStr"/>
-      <c r="J788" t="inlineStr"/>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K788" t="inlineStr"/>
       <c r="L788" t="inlineStr">
         <is>
@@ -54440,7 +57056,11 @@
       <c r="G789" t="inlineStr"/>
       <c r="H789" t="inlineStr"/>
       <c r="I789" t="inlineStr"/>
-      <c r="J789" t="inlineStr"/>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K789" t="inlineStr"/>
       <c r="L789" t="inlineStr">
         <is>
@@ -54501,7 +57121,11 @@
       <c r="G790" t="inlineStr"/>
       <c r="H790" t="inlineStr"/>
       <c r="I790" t="inlineStr"/>
-      <c r="J790" t="inlineStr"/>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K790" t="inlineStr"/>
       <c r="L790" t="inlineStr">
         <is>
@@ -54562,7 +57186,11 @@
       <c r="G791" t="inlineStr"/>
       <c r="H791" t="inlineStr"/>
       <c r="I791" t="inlineStr"/>
-      <c r="J791" t="inlineStr"/>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K791" t="inlineStr"/>
       <c r="L791" t="inlineStr">
         <is>
@@ -54623,7 +57251,11 @@
       <c r="G792" t="inlineStr"/>
       <c r="H792" t="inlineStr"/>
       <c r="I792" t="inlineStr"/>
-      <c r="J792" t="inlineStr"/>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K792" t="inlineStr"/>
       <c r="L792" t="inlineStr">
         <is>
@@ -54684,7 +57316,11 @@
       <c r="G793" t="inlineStr"/>
       <c r="H793" t="inlineStr"/>
       <c r="I793" t="inlineStr"/>
-      <c r="J793" t="inlineStr"/>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K793" t="inlineStr"/>
       <c r="L793" t="inlineStr">
         <is>
@@ -54745,7 +57381,11 @@
       <c r="G794" t="inlineStr"/>
       <c r="H794" t="inlineStr"/>
       <c r="I794" t="inlineStr"/>
-      <c r="J794" t="inlineStr"/>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K794" t="inlineStr"/>
       <c r="L794" t="inlineStr">
         <is>
@@ -54806,7 +57446,11 @@
       <c r="G795" t="inlineStr"/>
       <c r="H795" t="inlineStr"/>
       <c r="I795" t="inlineStr"/>
-      <c r="J795" t="inlineStr"/>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K795" t="inlineStr"/>
       <c r="L795" t="inlineStr">
         <is>
@@ -54867,7 +57511,11 @@
       <c r="G796" t="inlineStr"/>
       <c r="H796" t="inlineStr"/>
       <c r="I796" t="inlineStr"/>
-      <c r="J796" t="inlineStr"/>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K796" t="inlineStr"/>
       <c r="L796" t="inlineStr">
         <is>
@@ -54928,7 +57576,11 @@
       <c r="G797" t="inlineStr"/>
       <c r="H797" t="inlineStr"/>
       <c r="I797" t="inlineStr"/>
-      <c r="J797" t="inlineStr"/>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K797" t="inlineStr"/>
       <c r="L797" t="inlineStr">
         <is>
@@ -54989,7 +57641,11 @@
       <c r="G798" t="inlineStr"/>
       <c r="H798" t="inlineStr"/>
       <c r="I798" t="inlineStr"/>
-      <c r="J798" t="inlineStr"/>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K798" t="inlineStr"/>
       <c r="L798" t="inlineStr">
         <is>
@@ -55050,7 +57706,11 @@
       <c r="G799" t="inlineStr"/>
       <c r="H799" t="inlineStr"/>
       <c r="I799" t="inlineStr"/>
-      <c r="J799" t="inlineStr"/>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K799" t="inlineStr"/>
       <c r="L799" t="inlineStr">
         <is>
@@ -55111,7 +57771,11 @@
       <c r="G800" t="inlineStr"/>
       <c r="H800" t="inlineStr"/>
       <c r="I800" t="inlineStr"/>
-      <c r="J800" t="inlineStr"/>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K800" t="inlineStr"/>
       <c r="L800" t="inlineStr">
         <is>
@@ -55172,7 +57836,11 @@
       <c r="G801" t="inlineStr"/>
       <c r="H801" t="inlineStr"/>
       <c r="I801" t="inlineStr"/>
-      <c r="J801" t="inlineStr"/>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="K801" t="inlineStr"/>
       <c r="L801" t="inlineStr">
         <is>
